--- a/analysis_and_plots/pairwise_comparison_results.xlsx
+++ b/analysis_and_plots/pairwise_comparison_results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yaoyu\Documents\Epilepsy_research\FOS_analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yaoyu\Documents\Epilepsy_research\github_code\analysis_and_plots\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{22107DCB-4B1A-45C6-B5B7-A0402410C504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73C696C5-9634-4EE2-966D-FEADD8764FA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{2BA55BA8-6A9D-4C57-87A5-F6A1F27CBB68}"/>
+    <workbookView xWindow="19103" yWindow="-2093" windowWidth="23234" windowHeight="13876" xr2:uid="{2BA55BA8-6A9D-4C57-87A5-F6A1F27CBB68}"/>
   </bookViews>
   <sheets>
     <sheet name="pairwise_comparison_results" sheetId="1" r:id="rId1"/>
@@ -716,16 +716,14 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D76D00DB-3841-4FF6-ACCB-94E0FAAA6857}" name="Table1" displayName="Table1" ref="A1:F271" totalsRowShown="0" headerRowDxfId="0">
   <autoFilter ref="A1:F271" xr:uid="{D76D00DB-3841-4FF6-ACCB-94E0FAAA6857}">
-    <filterColumn colId="2">
+    <filterColumn colId="1">
       <filters>
-        <filter val="interictal vs ictal"/>
-        <filter val="interictal vs postictal"/>
-        <filter val="interictal vs preictal"/>
+        <filter val="alpha"/>
       </filters>
     </filterColumn>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F270">
-    <sortCondition ref="B1:B271"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F271">
+    <sortCondition ref="A1:A271"/>
   </sortState>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{27A11DAF-3C2E-4365-99BB-2228BD31592F}" name="patient"/>
@@ -1087,7 +1085,7 @@
         <v>2.9889999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -1149,82 +1147,82 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D6">
-        <v>0.66800000000000004</v>
+        <v>0.19500000000000001</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>1.6379999999999999</v>
+        <v>0.34499999999999997</v>
       </c>
     </row>
     <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7">
+        <v>0.17599999999999999</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0.30299999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8">
+        <v>0.89800000000000002</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>2.4039999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" t="s">
         <v>15</v>
       </c>
-      <c r="D7">
-        <v>0.48799999999999999</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0.94099999999999995</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8">
-        <v>0.40899999999999997</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0.93200000000000005</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" t="s">
-        <v>27</v>
-      </c>
       <c r="D9">
-        <v>0.307</v>
+        <v>0.85599999999999998</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>0.71899999999999997</v>
+        <v>1.9319999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
@@ -1232,19 +1230,19 @@
         <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="D10">
-        <v>0.19500000000000001</v>
+        <v>0.72199999999999998</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>0.34499999999999997</v>
+        <v>1.623</v>
       </c>
     </row>
     <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
@@ -1255,21 +1253,21 @@
         <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D11">
-        <v>0.17599999999999999</v>
+        <v>0.64400000000000002</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11">
-        <v>0.30299999999999999</v>
+        <v>1.431</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
         <v>14</v>
@@ -1278,36 +1276,36 @@
         <v>22</v>
       </c>
       <c r="D12">
-        <v>0.81799999999999995</v>
+        <v>0.66800000000000004</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12">
-        <v>2.5640000000000001</v>
+        <v>1.6379999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D13">
-        <v>0.72199999999999998</v>
+        <v>0.48799999999999999</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13">
-        <v>2.0910000000000002</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>0.94099999999999995</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>30</v>
       </c>
@@ -1315,21 +1313,21 @@
         <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D14">
-        <v>0.628</v>
+        <v>0.40899999999999997</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>1.6359999999999999</v>
+        <v>0.93200000000000005</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B15" t="s">
         <v>14</v>
@@ -1338,158 +1336,158 @@
         <v>27</v>
       </c>
       <c r="D15">
-        <v>0.503</v>
+        <v>0.307</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15">
-        <v>1.2989999999999999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>0.71899999999999997</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
         <v>10</v>
       </c>
       <c r="D16">
-        <v>0.55100000000000005</v>
+        <v>0.628</v>
       </c>
       <c r="E16">
         <v>0</v>
       </c>
       <c r="F16">
-        <v>1.2669999999999999</v>
+        <v>1.6359999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C17" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D17">
-        <v>0.55300000000000005</v>
+        <v>0.55100000000000005</v>
       </c>
       <c r="E17">
         <v>0</v>
       </c>
       <c r="F17">
-        <v>1.0429999999999999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1.2669999999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B18" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C18" t="s">
         <v>22</v>
       </c>
       <c r="D18">
-        <v>0.82699999999999996</v>
+        <v>0.78</v>
       </c>
       <c r="E18">
         <v>0</v>
       </c>
       <c r="F18">
-        <v>2.8319999999999999</v>
+        <v>1.714</v>
       </c>
     </row>
     <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C19" t="s">
         <v>15</v>
       </c>
       <c r="D19">
-        <v>0.71799999999999997</v>
+        <v>0.73499999999999999</v>
       </c>
       <c r="E19">
         <v>0</v>
       </c>
       <c r="F19">
-        <v>1.996</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1.4610000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20">
+        <v>0.29699999999999999</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0.65600000000000003</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" t="s">
         <v>27</v>
       </c>
-      <c r="D20">
-        <v>0.51900000000000002</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>1.377</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>35</v>
-      </c>
-      <c r="B21" t="s">
-        <v>14</v>
-      </c>
-      <c r="C21" t="s">
-        <v>8</v>
-      </c>
       <c r="D21">
-        <v>0.27100000000000002</v>
+        <v>0.26900000000000002</v>
       </c>
       <c r="E21">
         <v>0</v>
       </c>
       <c r="F21">
-        <v>0.56200000000000006</v>
+        <v>0.64400000000000002</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B22" t="s">
         <v>14</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D22">
-        <v>0.54600000000000004</v>
+        <v>0.81799999999999995</v>
       </c>
       <c r="E22">
         <v>0</v>
       </c>
       <c r="F22">
-        <v>1.506</v>
+        <v>2.5640000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B23" t="s">
         <v>14</v>
@@ -1498,38 +1496,38 @@
         <v>8</v>
       </c>
       <c r="D23">
-        <v>0.46100000000000002</v>
+        <v>0.72199999999999998</v>
       </c>
       <c r="E23">
         <v>0</v>
       </c>
       <c r="F23">
-        <v>1.228</v>
+        <v>2.0910000000000002</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B24" t="s">
         <v>14</v>
       </c>
       <c r="C24" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D24">
-        <v>0.56599999999999995</v>
+        <v>0.503</v>
       </c>
       <c r="E24">
         <v>0</v>
       </c>
       <c r="F24">
-        <v>1.1479999999999999</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>1.2989999999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B25" t="s">
         <v>14</v>
@@ -1538,93 +1536,93 @@
         <v>15</v>
       </c>
       <c r="D25">
-        <v>0.182</v>
+        <v>0.55300000000000005</v>
       </c>
       <c r="E25">
         <v>0</v>
       </c>
       <c r="F25">
-        <v>0.17299999999999999</v>
+        <v>1.0429999999999999</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B26" t="s">
         <v>14</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="D26">
-        <v>0.89600000000000002</v>
+        <v>0.34</v>
       </c>
       <c r="E26">
         <v>0</v>
       </c>
       <c r="F26">
-        <v>3.335</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C27" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D27">
-        <v>0.74</v>
+        <v>0.30399999999999999</v>
       </c>
       <c r="E27">
         <v>0</v>
       </c>
       <c r="F27">
-        <v>2.125</v>
+        <v>0.69099999999999995</v>
       </c>
     </row>
     <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B28" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C28" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D28">
-        <v>0.42499999999999999</v>
+        <v>0.86699999999999999</v>
       </c>
       <c r="E28">
         <v>0</v>
       </c>
       <c r="F28">
-        <v>1.0509999999999999</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+        <v>2.3889999999999998</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B29" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C29" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D29">
-        <v>0.40500000000000003</v>
+        <v>0.76100000000000001</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29">
-        <v>0.94799999999999995</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
@@ -1632,19 +1630,19 @@
         <v>32</v>
       </c>
       <c r="B30" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C30" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D30">
-        <v>0.34</v>
+        <v>0.81799999999999995</v>
       </c>
       <c r="E30">
         <v>0</v>
       </c>
       <c r="F30">
-        <v>0.91</v>
+        <v>1.702</v>
       </c>
     </row>
     <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
@@ -1655,99 +1653,99 @@
         <v>7</v>
       </c>
       <c r="C31" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="D31">
-        <v>0.30399999999999999</v>
+        <v>0.58199999999999996</v>
       </c>
       <c r="E31">
         <v>0</v>
       </c>
       <c r="F31">
-        <v>0.69099999999999995</v>
+        <v>1.3520000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="B32" t="s">
         <v>14</v>
       </c>
       <c r="C32" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D32">
-        <v>0.81899999999999995</v>
+        <v>0.82699999999999996</v>
       </c>
       <c r="E32">
         <v>0</v>
       </c>
       <c r="F32">
-        <v>3.02</v>
+        <v>2.8319999999999999</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="B33" t="s">
         <v>14</v>
       </c>
       <c r="C33" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D33">
-        <v>0.83699999999999997</v>
+        <v>0.71799999999999997</v>
       </c>
       <c r="E33">
         <v>0</v>
       </c>
       <c r="F33">
-        <v>2.984</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>1.996</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="B34" t="s">
         <v>14</v>
       </c>
       <c r="C34" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="D34">
-        <v>0.70099999999999996</v>
+        <v>0.51900000000000002</v>
       </c>
       <c r="E34">
         <v>0</v>
       </c>
       <c r="F34">
-        <v>2.0350000000000001</v>
+        <v>1.377</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="B35" t="s">
         <v>14</v>
       </c>
       <c r="C35" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D35">
-        <v>0.53300000000000003</v>
+        <v>0.27100000000000002</v>
       </c>
       <c r="E35">
         <v>0</v>
       </c>
       <c r="F35">
-        <v>1.1830000000000001</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>0.56200000000000006</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>35</v>
       </c>
@@ -1787,89 +1785,89 @@
         <v>1.5609999999999999</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C38" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D38">
-        <v>0.97599999999999998</v>
+        <v>0.86899999999999999</v>
       </c>
       <c r="E38">
         <v>0</v>
       </c>
       <c r="F38">
-        <v>4.117</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+        <v>2.3410000000000002</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="B39" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C39" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D39">
-        <v>0.98</v>
+        <v>0.81399999999999995</v>
       </c>
       <c r="E39">
         <v>0</v>
       </c>
       <c r="F39">
-        <v>3.9910000000000001</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1.9490000000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="B40" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C40" t="s">
         <v>27</v>
       </c>
       <c r="D40">
-        <v>0.97399999999999998</v>
+        <v>0.46400000000000002</v>
       </c>
       <c r="E40">
         <v>0</v>
       </c>
       <c r="F40">
-        <v>3.879</v>
+        <v>1.234</v>
       </c>
     </row>
     <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
-        <v>9</v>
+      <c r="A41" t="s">
+        <v>35</v>
       </c>
       <c r="B41" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C41" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D41">
-        <v>5.0999999999999997E-2</v>
+        <v>0.29199999999999998</v>
       </c>
       <c r="E41">
-        <v>2.2200000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="F41">
-        <v>1.7999999999999999E-2</v>
+        <v>0.49299999999999999</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="B42" t="s">
         <v>14</v>
@@ -1878,58 +1876,58 @@
         <v>27</v>
       </c>
       <c r="D42">
-        <v>0.60399999999999998</v>
+        <v>0.54600000000000004</v>
       </c>
       <c r="E42">
         <v>0</v>
       </c>
       <c r="F42">
-        <v>1.7410000000000001</v>
+        <v>1.506</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="B43" t="s">
         <v>14</v>
       </c>
       <c r="C43" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D43">
-        <v>0.60899999999999999</v>
+        <v>0.46100000000000002</v>
       </c>
       <c r="E43">
         <v>0</v>
       </c>
       <c r="F43">
-        <v>1.722</v>
+        <v>1.228</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="B44" t="s">
         <v>14</v>
       </c>
       <c r="C44" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D44">
-        <v>0.58399999999999996</v>
+        <v>0.56599999999999995</v>
       </c>
       <c r="E44">
         <v>0</v>
       </c>
       <c r="F44">
-        <v>1.651</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
-        <v>19</v>
+        <v>1.1479999999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>37</v>
       </c>
       <c r="B45" t="s">
         <v>14</v>
@@ -1938,73 +1936,73 @@
         <v>15</v>
       </c>
       <c r="D45">
-        <v>5.5E-2</v>
+        <v>0.182</v>
       </c>
       <c r="E45">
-        <v>1.0500000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="F45">
-        <v>9.7000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0.17299999999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="B46" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C46" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D46">
-        <v>0.71299999999999997</v>
+        <v>0.14199999999999999</v>
       </c>
       <c r="E46">
         <v>0</v>
       </c>
       <c r="F46">
-        <v>2.0569999999999999</v>
+        <v>0.26100000000000001</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="B47" t="s">
         <v>14</v>
       </c>
       <c r="C47" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="D47">
-        <v>0.70199999999999996</v>
+        <v>0.10199999999999999</v>
       </c>
       <c r="E47">
         <v>0</v>
       </c>
       <c r="F47">
-        <v>1.976</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0.184</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="B48" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C48" t="s">
         <v>22</v>
       </c>
       <c r="D48">
-        <v>0.69099999999999995</v>
+        <v>0.67300000000000004</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48">
-        <v>1.966</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
@@ -2015,16 +2013,16 @@
         <v>7</v>
       </c>
       <c r="C49" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="D49">
-        <v>0.14199999999999999</v>
+        <v>0.60199999999999998</v>
       </c>
       <c r="E49">
         <v>0</v>
       </c>
       <c r="F49">
-        <v>0.26100000000000001</v>
+        <v>1.431</v>
       </c>
     </row>
     <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
@@ -2032,44 +2030,44 @@
         <v>37</v>
       </c>
       <c r="B50" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C50" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D50">
-        <v>0.10199999999999999</v>
+        <v>0.51600000000000001</v>
       </c>
       <c r="E50">
         <v>0</v>
       </c>
       <c r="F50">
-        <v>0.184</v>
+        <v>1.161</v>
       </c>
     </row>
     <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
-        <v>13</v>
+      <c r="A51" t="s">
+        <v>37</v>
       </c>
       <c r="B51" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C51" t="s">
         <v>15</v>
       </c>
       <c r="D51">
-        <v>4.7E-2</v>
+        <v>0.53800000000000003</v>
       </c>
       <c r="E51">
-        <v>4.8399999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="F51">
-        <v>3.1E-2</v>
+        <v>0.88600000000000001</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B52" t="s">
         <v>14</v>
@@ -2078,153 +2076,153 @@
         <v>27</v>
       </c>
       <c r="D52">
-        <v>0.69</v>
+        <v>0.89600000000000002</v>
       </c>
       <c r="E52">
         <v>0</v>
       </c>
       <c r="F52">
-        <v>2.238</v>
+        <v>3.335</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B53" t="s">
         <v>14</v>
       </c>
       <c r="C53" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D53">
-        <v>0.67400000000000004</v>
+        <v>0.74</v>
       </c>
       <c r="E53">
         <v>0</v>
       </c>
       <c r="F53">
-        <v>2.0880000000000001</v>
+        <v>2.125</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B54" t="s">
         <v>14</v>
       </c>
       <c r="C54" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D54">
-        <v>0.57699999999999996</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="E54">
         <v>0</v>
       </c>
       <c r="F54">
-        <v>1.69</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>1.0509999999999999</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B55" t="s">
         <v>14</v>
       </c>
       <c r="C55" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D55">
-        <v>0.14799999999999999</v>
+        <v>0.40500000000000003</v>
       </c>
       <c r="E55">
         <v>0</v>
       </c>
       <c r="F55">
-        <v>0.443</v>
+        <v>0.94799999999999995</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="B56" t="s">
         <v>14</v>
       </c>
       <c r="C56" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D56">
-        <v>0.74</v>
+        <v>0.30599999999999999</v>
       </c>
       <c r="E56">
         <v>0</v>
       </c>
       <c r="F56">
-        <v>2.33</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0.71399999999999997</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="B57" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C57" t="s">
+        <v>10</v>
+      </c>
+      <c r="D57">
+        <v>0.316</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>38</v>
+      </c>
+      <c r="B58" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" t="s">
         <v>27</v>
       </c>
-      <c r="D57">
-        <v>0.72199999999999998</v>
-      </c>
-      <c r="E57">
-        <v>0</v>
-      </c>
-      <c r="F57">
-        <v>2.145</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>11</v>
-      </c>
-      <c r="B58" t="s">
-        <v>14</v>
-      </c>
-      <c r="C58" t="s">
-        <v>22</v>
-      </c>
       <c r="D58">
-        <v>0.63300000000000001</v>
+        <v>0.93400000000000005</v>
       </c>
       <c r="E58">
         <v>0</v>
       </c>
       <c r="F58">
-        <v>1.7050000000000001</v>
+        <v>3.0379999999999998</v>
       </c>
     </row>
     <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="B59" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C59" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D59">
-        <v>0.23300000000000001</v>
+        <v>0.78500000000000003</v>
       </c>
       <c r="E59">
         <v>0</v>
       </c>
       <c r="F59">
-        <v>0.43099999999999999</v>
+        <v>2.2309999999999999</v>
       </c>
     </row>
     <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
@@ -2232,19 +2230,19 @@
         <v>38</v>
       </c>
       <c r="B60" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C60" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D60">
-        <v>0.30599999999999999</v>
+        <v>0.47499999999999998</v>
       </c>
       <c r="E60">
         <v>0</v>
       </c>
       <c r="F60">
-        <v>0.71399999999999997</v>
+        <v>1.0109999999999999</v>
       </c>
     </row>
     <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
@@ -2255,41 +2253,41 @@
         <v>7</v>
       </c>
       <c r="C61" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D61">
-        <v>0.316</v>
+        <v>0.45900000000000002</v>
       </c>
       <c r="E61">
         <v>0</v>
       </c>
       <c r="F61">
-        <v>0.52</v>
+        <v>0.96199999999999997</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B62" t="s">
         <v>14</v>
       </c>
       <c r="C62" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D62">
-        <v>0.96499999999999997</v>
+        <v>0.81899999999999995</v>
       </c>
       <c r="E62">
         <v>0</v>
       </c>
       <c r="F62">
-        <v>5.0110000000000001</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B63" t="s">
         <v>14</v>
@@ -2298,133 +2296,133 @@
         <v>8</v>
       </c>
       <c r="D63">
-        <v>0.86199999999999999</v>
+        <v>0.83699999999999997</v>
       </c>
       <c r="E63">
         <v>0</v>
       </c>
       <c r="F63">
-        <v>3.234</v>
+        <v>2.984</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B64" t="s">
         <v>14</v>
       </c>
       <c r="C64" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="D64">
-        <v>0.83099999999999996</v>
+        <v>0.70099999999999996</v>
       </c>
       <c r="E64">
         <v>0</v>
       </c>
       <c r="F64">
-        <v>3.0289999999999999</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+        <v>2.0350000000000001</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B65" t="s">
         <v>14</v>
       </c>
       <c r="C65" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D65">
-        <v>0.84899999999999998</v>
+        <v>0.53300000000000003</v>
       </c>
       <c r="E65">
         <v>0</v>
       </c>
       <c r="F65">
-        <v>2.3610000000000002</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1.1830000000000001</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="B66" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C66" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D66">
-        <v>0.93200000000000005</v>
+        <v>7.2999999999999995E-2</v>
       </c>
       <c r="E66">
-        <v>0</v>
+        <v>4.8999999999999998E-3</v>
       </c>
       <c r="F66">
-        <v>4.6050000000000004</v>
+        <v>0.127</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="B67" t="s">
         <v>14</v>
       </c>
       <c r="C67" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D67">
-        <v>0.9</v>
+        <v>8.2000000000000003E-2</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>1E-3</v>
       </c>
       <c r="F67">
-        <v>3.391</v>
+        <v>5.7000000000000002E-2</v>
       </c>
     </row>
     <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="B68" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C68" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D68">
-        <v>0.89600000000000002</v>
+        <v>0.86299999999999999</v>
       </c>
       <c r="E68">
         <v>0</v>
       </c>
       <c r="F68">
-        <v>2.85</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+        <v>3.0390000000000001</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="B69" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C69" t="s">
         <v>27</v>
       </c>
       <c r="D69">
-        <v>0.78200000000000003</v>
+        <v>0.83799999999999997</v>
       </c>
       <c r="E69">
         <v>0</v>
       </c>
       <c r="F69">
-        <v>2.6629999999999998</v>
+        <v>3.0089999999999999</v>
       </c>
     </row>
     <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
@@ -2435,16 +2433,16 @@
         <v>7</v>
       </c>
       <c r="C70" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D70">
-        <v>7.2999999999999995E-2</v>
+        <v>0.85299999999999998</v>
       </c>
       <c r="E70">
-        <v>4.8999999999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="F70">
-        <v>0.127</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
@@ -2452,44 +2450,44 @@
         <v>25</v>
       </c>
       <c r="B71" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C71" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D71">
-        <v>8.2000000000000003E-2</v>
+        <v>0.52100000000000002</v>
       </c>
       <c r="E71">
-        <v>1E-3</v>
+        <v>0</v>
       </c>
       <c r="F71">
-        <v>5.7000000000000002E-2</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+        <v>0.79900000000000004</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B72" t="s">
         <v>14</v>
       </c>
       <c r="C72" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D72">
-        <v>0.52800000000000002</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="E72">
         <v>0</v>
       </c>
       <c r="F72">
-        <v>1.147</v>
+        <v>4.117</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B73" t="s">
         <v>14</v>
@@ -2498,13 +2496,13 @@
         <v>22</v>
       </c>
       <c r="D73">
-        <v>0.46600000000000003</v>
+        <v>0.98</v>
       </c>
       <c r="E73">
         <v>0</v>
       </c>
       <c r="F73">
-        <v>0.89800000000000002</v>
+        <v>3.9910000000000001</v>
       </c>
       <c r="I73" t="s">
         <v>36</v>
@@ -2512,7 +2510,7 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B74" t="s">
         <v>14</v>
@@ -2521,73 +2519,73 @@
         <v>27</v>
       </c>
       <c r="D74">
-        <v>0.27600000000000002</v>
+        <v>0.97399999999999998</v>
       </c>
       <c r="E74">
         <v>0</v>
       </c>
       <c r="F74">
-        <v>0.58899999999999997</v>
+        <v>3.879</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>6</v>
+      <c r="A75" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="B75" t="s">
         <v>14</v>
       </c>
       <c r="C75" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D75">
-        <v>0.161</v>
+        <v>5.0999999999999997E-2</v>
       </c>
       <c r="E75">
-        <v>0</v>
+        <v>2.2200000000000001E-2</v>
       </c>
       <c r="F75">
-        <v>0.37</v>
+        <v>1.7999999999999999E-2</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B76" t="s">
         <v>14</v>
       </c>
       <c r="C76" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="D76">
-        <v>0.443</v>
+        <v>0.13</v>
       </c>
       <c r="E76">
         <v>0</v>
       </c>
       <c r="F76">
-        <v>1.0720000000000001</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>28</v>
+        <v>0.224</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="B77" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C77" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D77">
-        <v>0.24199999999999999</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="E77">
-        <v>0</v>
+        <v>0.34279999999999999</v>
       </c>
       <c r="F77">
-        <v>0.47499999999999998</v>
+        <v>1.4E-2</v>
       </c>
     </row>
     <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
@@ -2595,59 +2593,59 @@
         <v>9</v>
       </c>
       <c r="B78" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C78" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D78">
-        <v>0.13</v>
+        <v>0.85099999999999998</v>
       </c>
       <c r="E78">
         <v>0</v>
       </c>
       <c r="F78">
-        <v>0.224</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1.367</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B79" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C79" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D79">
-        <v>0.112</v>
+        <v>0.86899999999999999</v>
       </c>
       <c r="E79">
-        <v>1E-4</v>
+        <v>0</v>
       </c>
       <c r="F79">
-        <v>0.23699999999999999</v>
+        <v>1.365</v>
       </c>
     </row>
     <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B80" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C80" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D80">
-        <v>0.189</v>
+        <v>0.85099999999999998</v>
       </c>
       <c r="E80">
         <v>0</v>
       </c>
       <c r="F80">
-        <v>0.21</v>
+        <v>1.361</v>
       </c>
     </row>
     <row r="81" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
@@ -2658,61 +2656,61 @@
         <v>7</v>
       </c>
       <c r="C81" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D81">
-        <v>3.2000000000000001E-2</v>
+        <v>4.2000000000000003E-2</v>
       </c>
       <c r="E81">
-        <v>0.34279999999999999</v>
+        <v>9.8199999999999996E-2</v>
       </c>
       <c r="F81">
-        <v>1.4E-2</v>
+        <v>4.5999999999999999E-2</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B82" t="s">
         <v>14</v>
       </c>
       <c r="C82" t="s">
+        <v>27</v>
+      </c>
+      <c r="D82">
+        <v>0.60399999999999998</v>
+      </c>
+      <c r="E82">
+        <v>0</v>
+      </c>
+      <c r="F82">
+        <v>1.7410000000000001</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>19</v>
+      </c>
+      <c r="B83" t="s">
+        <v>14</v>
+      </c>
+      <c r="C83" t="s">
         <v>22</v>
       </c>
-      <c r="D82">
-        <v>0.76</v>
-      </c>
-      <c r="E82">
-        <v>0</v>
-      </c>
-      <c r="F82">
-        <v>2.1720000000000002</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
-        <v>31</v>
-      </c>
-      <c r="B83" t="s">
-        <v>14</v>
-      </c>
-      <c r="C83" t="s">
-        <v>15</v>
-      </c>
       <c r="D83">
-        <v>0.49399999999999999</v>
+        <v>0.60899999999999999</v>
       </c>
       <c r="E83">
         <v>0</v>
       </c>
       <c r="F83">
-        <v>1.292</v>
+        <v>1.722</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B84" t="s">
         <v>14</v>
@@ -2721,73 +2719,73 @@
         <v>8</v>
       </c>
       <c r="D84">
-        <v>0.32</v>
+        <v>0.58399999999999996</v>
       </c>
       <c r="E84">
         <v>0</v>
       </c>
       <c r="F84">
-        <v>0.63200000000000001</v>
+        <v>1.651</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
-        <v>31</v>
+      <c r="A85" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="B85" t="s">
         <v>14</v>
       </c>
       <c r="C85" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="D85">
-        <v>0.14499999999999999</v>
+        <v>5.5E-2</v>
       </c>
       <c r="E85">
-        <v>0</v>
+        <v>1.0500000000000001E-2</v>
       </c>
       <c r="F85">
-        <v>0.29699999999999999</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>9.7000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B86" t="s">
         <v>14</v>
       </c>
       <c r="C86" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D86">
-        <v>0.747</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="E86">
-        <v>0</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="F86">
-        <v>2.1850000000000001</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0.106</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B87" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C87" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D87">
-        <v>0.64900000000000002</v>
+        <v>6.4000000000000001E-2</v>
       </c>
       <c r="E87">
-        <v>0</v>
+        <v>1.8E-3</v>
       </c>
       <c r="F87">
-        <v>1.7170000000000001</v>
+        <v>8.6999999999999994E-2</v>
       </c>
     </row>
     <row r="88" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
@@ -2795,39 +2793,39 @@
         <v>19</v>
       </c>
       <c r="B88" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C88" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D88">
-        <v>7.0000000000000007E-2</v>
+        <v>0.20799999999999999</v>
       </c>
       <c r="E88">
-        <v>5.0000000000000001E-4</v>
+        <v>0</v>
       </c>
       <c r="F88">
-        <v>0.106</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0.20200000000000001</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B89" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C89" t="s">
         <v>8</v>
       </c>
       <c r="D89">
-        <v>0.245</v>
+        <v>0.23400000000000001</v>
       </c>
       <c r="E89">
         <v>0</v>
       </c>
       <c r="F89">
-        <v>0.53</v>
+        <v>0.182</v>
       </c>
     </row>
     <row r="90" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
@@ -2838,41 +2836,41 @@
         <v>7</v>
       </c>
       <c r="C90" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="D90">
-        <v>6.4000000000000001E-2</v>
+        <v>0.23400000000000001</v>
       </c>
       <c r="E90">
-        <v>1.8E-3</v>
+        <v>0</v>
       </c>
       <c r="F90">
-        <v>8.6999999999999994E-2</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
-        <v>17</v>
+        <v>0.14399999999999999</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="B91" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C91" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="D91">
-        <v>0.214</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="E91">
-        <v>0</v>
+        <v>5.8200000000000002E-2</v>
       </c>
       <c r="F91">
-        <v>0.46899999999999997</v>
+        <v>4.4999999999999998E-2</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B92" t="s">
         <v>14</v>
@@ -2881,18 +2879,18 @@
         <v>8</v>
       </c>
       <c r="D92">
-        <v>0.58899999999999997</v>
+        <v>0.71299999999999997</v>
       </c>
       <c r="E92">
         <v>0</v>
       </c>
       <c r="F92">
-        <v>1.5069999999999999</v>
+        <v>2.0569999999999999</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B93" t="s">
         <v>14</v>
@@ -2901,113 +2899,113 @@
         <v>27</v>
       </c>
       <c r="D93">
-        <v>0.54800000000000004</v>
+        <v>0.70199999999999996</v>
       </c>
       <c r="E93">
         <v>0</v>
       </c>
       <c r="F93">
-        <v>1.4019999999999999</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>1.976</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B94" t="s">
         <v>14</v>
       </c>
       <c r="C94" t="s">
+        <v>22</v>
+      </c>
+      <c r="D94">
+        <v>0.69099999999999995</v>
+      </c>
+      <c r="E94">
+        <v>0</v>
+      </c>
+      <c r="F94">
+        <v>1.966</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B95" t="s">
+        <v>14</v>
+      </c>
+      <c r="C95" t="s">
         <v>15</v>
       </c>
-      <c r="D94">
-        <v>0.32300000000000001</v>
-      </c>
-      <c r="E94">
-        <v>0</v>
-      </c>
-      <c r="F94">
-        <v>0.83299999999999996</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
-        <v>12</v>
-      </c>
-      <c r="B95" t="s">
-        <v>14</v>
-      </c>
-      <c r="C95" t="s">
-        <v>22</v>
-      </c>
       <c r="D95">
-        <v>0.28699999999999998</v>
+        <v>4.7E-2</v>
       </c>
       <c r="E95">
-        <v>0</v>
+        <v>4.8399999999999999E-2</v>
       </c>
       <c r="F95">
-        <v>0.55700000000000005</v>
+        <v>3.1E-2</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="B96" t="s">
         <v>14</v>
       </c>
       <c r="C96" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D96">
-        <v>0.629</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="E96">
-        <v>0</v>
+        <v>1.5E-3</v>
       </c>
       <c r="F96">
-        <v>1.6579999999999999</v>
+        <v>6.6000000000000003E-2</v>
       </c>
     </row>
     <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
-        <v>34</v>
+      <c r="A97" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="B97" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C97" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D97">
-        <v>0.55100000000000005</v>
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="E97">
-        <v>0</v>
+        <v>0.1714</v>
       </c>
       <c r="F97">
-        <v>1.286</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+        <v>3.5000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="B98" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C98" t="s">
         <v>27</v>
       </c>
       <c r="D98">
-        <v>0.247</v>
+        <v>0.38700000000000001</v>
       </c>
       <c r="E98">
         <v>0</v>
       </c>
       <c r="F98">
-        <v>0.56899999999999995</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
@@ -3015,84 +3013,84 @@
         <v>13</v>
       </c>
       <c r="B99" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C99" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D99">
-        <v>6.5000000000000002E-2</v>
+        <v>0.377</v>
       </c>
       <c r="E99">
-        <v>1.5E-3</v>
+        <v>0</v>
       </c>
       <c r="F99">
-        <v>6.6000000000000003E-2</v>
+        <v>0.25900000000000001</v>
       </c>
     </row>
     <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="2" t="s">
+      <c r="A100" t="s">
         <v>13</v>
       </c>
       <c r="B100" t="s">
         <v>7</v>
       </c>
       <c r="C100" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D100">
-        <v>3.7999999999999999E-2</v>
+        <v>0.34699999999999998</v>
       </c>
       <c r="E100">
-        <v>0.1714</v>
+        <v>0</v>
       </c>
       <c r="F100">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0.22800000000000001</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="B101" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C101" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D101">
-        <v>0.193</v>
+        <v>6.8000000000000005E-2</v>
       </c>
       <c r="E101">
-        <v>0</v>
+        <v>6.9999999999999999E-4</v>
       </c>
       <c r="F101">
-        <v>0.39700000000000002</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>8.5999999999999993E-2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="B102" t="s">
         <v>14</v>
       </c>
       <c r="C102" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="D102">
-        <v>0.81599999999999995</v>
+        <v>0.69</v>
       </c>
       <c r="E102">
         <v>0</v>
       </c>
       <c r="F102">
-        <v>2.2869999999999999</v>
+        <v>2.238</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="B103" t="s">
         <v>14</v>
@@ -3101,36 +3099,36 @@
         <v>22</v>
       </c>
       <c r="D103">
-        <v>0.64100000000000001</v>
+        <v>0.67400000000000004</v>
       </c>
       <c r="E103">
         <v>0</v>
       </c>
       <c r="F103">
-        <v>1.7110000000000001</v>
+        <v>2.0880000000000001</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="B104" t="s">
         <v>14</v>
       </c>
       <c r="C104" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="D104">
-        <v>0.375</v>
+        <v>0.57699999999999996</v>
       </c>
       <c r="E104">
         <v>0</v>
       </c>
       <c r="F104">
-        <v>0.90300000000000002</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>1.69</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>39</v>
       </c>
@@ -3138,56 +3136,56 @@
         <v>14</v>
       </c>
       <c r="C105" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D105">
-        <v>0.26900000000000002</v>
+        <v>0.14799999999999999</v>
       </c>
       <c r="E105">
         <v>0</v>
       </c>
       <c r="F105">
-        <v>0.55600000000000005</v>
+        <v>0.443</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="B106" t="s">
         <v>14</v>
       </c>
       <c r="C106" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D106">
-        <v>0.33500000000000002</v>
+        <v>0.26900000000000002</v>
       </c>
       <c r="E106">
         <v>0</v>
       </c>
       <c r="F106">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0.55600000000000005</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B107" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C107" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="D107">
-        <v>0.66600000000000004</v>
+        <v>0.127</v>
       </c>
       <c r="E107">
         <v>0</v>
       </c>
       <c r="F107">
-        <v>1.833</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="108" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
@@ -3198,236 +3196,236 @@
         <v>7</v>
       </c>
       <c r="C108" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D108">
-        <v>0.127</v>
+        <v>0.377</v>
       </c>
       <c r="E108">
         <v>0</v>
       </c>
       <c r="F108">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0.29599999999999999</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B109" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C109" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="D109">
-        <v>0.59699999999999998</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="E109">
         <v>0</v>
       </c>
       <c r="F109">
-        <v>1.4970000000000001</v>
+        <v>0.22500000000000001</v>
       </c>
     </row>
     <row r="110" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B110" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C110" t="s">
+        <v>22</v>
+      </c>
+      <c r="D110">
+        <v>0.317</v>
+      </c>
+      <c r="E110">
+        <v>0</v>
+      </c>
+      <c r="F110">
+        <v>0.224</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>39</v>
+      </c>
+      <c r="B111" t="s">
+        <v>7</v>
+      </c>
+      <c r="C111" t="s">
         <v>15</v>
       </c>
-      <c r="D110">
-        <v>0.52200000000000002</v>
-      </c>
-      <c r="E110">
-        <v>0</v>
-      </c>
-      <c r="F110">
-        <v>1.2869999999999999</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
-        <v>33</v>
-      </c>
-      <c r="B111" t="s">
-        <v>14</v>
-      </c>
-      <c r="C111" t="s">
-        <v>22</v>
-      </c>
       <c r="D111">
-        <v>0.153</v>
+        <v>0.10199999999999999</v>
       </c>
       <c r="E111">
         <v>0</v>
       </c>
       <c r="F111">
-        <v>7.0999999999999994E-2</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B112" t="s">
         <v>14</v>
       </c>
       <c r="C112" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D112">
-        <v>0.29699999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="E112">
         <v>0</v>
       </c>
       <c r="F112">
-        <v>0.61699999999999999</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B113" t="s">
         <v>14</v>
       </c>
       <c r="C113" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D113">
-        <v>0.26200000000000001</v>
+        <v>0.72199999999999998</v>
       </c>
       <c r="E113">
         <v>0</v>
       </c>
       <c r="F113">
-        <v>0.44500000000000001</v>
+        <v>2.145</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B114" t="s">
         <v>14</v>
       </c>
       <c r="C114" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D114">
-        <v>0.113</v>
+        <v>0.63300000000000001</v>
       </c>
       <c r="E114">
         <v>0</v>
       </c>
       <c r="F114">
-        <v>0.214</v>
+        <v>1.7050000000000001</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B115" t="s">
         <v>14</v>
       </c>
       <c r="C115" t="s">
+        <v>15</v>
+      </c>
+      <c r="D115">
+        <v>0.23300000000000001</v>
+      </c>
+      <c r="E115">
+        <v>0</v>
+      </c>
+      <c r="F115">
+        <v>0.43099999999999999</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>11</v>
+      </c>
+      <c r="B116" t="s">
+        <v>14</v>
+      </c>
+      <c r="C116" t="s">
+        <v>10</v>
+      </c>
+      <c r="D116">
+        <v>9.0999999999999998E-2</v>
+      </c>
+      <c r="E116">
+        <v>0</v>
+      </c>
+      <c r="F116">
+        <v>0.14499999999999999</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B117" t="s">
+        <v>7</v>
+      </c>
+      <c r="C117" t="s">
+        <v>10</v>
+      </c>
+      <c r="D117">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="E117">
+        <v>0.26369999999999999</v>
+      </c>
+      <c r="F117">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>11</v>
+      </c>
+      <c r="B118" t="s">
+        <v>7</v>
+      </c>
+      <c r="C118" t="s">
         <v>8</v>
       </c>
-      <c r="D115">
-        <v>7.5999999999999998E-2</v>
-      </c>
-      <c r="E115">
-        <v>3.0999999999999999E-3</v>
-      </c>
-      <c r="F115">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
-        <v>21</v>
-      </c>
-      <c r="B116" t="s">
-        <v>14</v>
-      </c>
-      <c r="C116" t="s">
-        <v>15</v>
-      </c>
-      <c r="D116">
-        <v>0.10199999999999999</v>
-      </c>
-      <c r="E116">
-        <v>0</v>
-      </c>
-      <c r="F116">
-        <v>0.17899999999999999</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
-        <v>21</v>
-      </c>
-      <c r="B117" t="s">
-        <v>14</v>
-      </c>
-      <c r="C117" t="s">
+      <c r="D118">
+        <v>0.621</v>
+      </c>
+      <c r="E118">
+        <v>0</v>
+      </c>
+      <c r="F118">
+        <v>0.66200000000000003</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>11</v>
+      </c>
+      <c r="B119" t="s">
+        <v>7</v>
+      </c>
+      <c r="C119" t="s">
         <v>27</v>
       </c>
-      <c r="D117">
-        <v>0.105</v>
-      </c>
-      <c r="E117">
-        <v>0</v>
-      </c>
-      <c r="F117">
-        <v>0.17499999999999999</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B118" t="s">
-        <v>14</v>
-      </c>
-      <c r="C118" t="s">
-        <v>22</v>
-      </c>
-      <c r="D118">
-        <v>6.3E-2</v>
-      </c>
-      <c r="E118">
-        <v>2.2200000000000001E-2</v>
-      </c>
-      <c r="F118">
-        <v>0.121</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" t="s">
-        <v>21</v>
-      </c>
-      <c r="B119" t="s">
-        <v>14</v>
-      </c>
-      <c r="C119" t="s">
-        <v>8</v>
-      </c>
       <c r="D119">
-        <v>8.3000000000000004E-2</v>
+        <v>0.624</v>
       </c>
       <c r="E119">
-        <v>8.9999999999999998E-4</v>
+        <v>0</v>
       </c>
       <c r="F119">
-        <v>7.3999999999999996E-2</v>
+        <v>0.65800000000000003</v>
       </c>
     </row>
     <row r="120" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
@@ -3435,44 +3433,44 @@
         <v>11</v>
       </c>
       <c r="B120" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C120" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D120">
-        <v>9.0999999999999998E-2</v>
+        <v>0.52900000000000003</v>
       </c>
       <c r="E120">
         <v>0</v>
       </c>
       <c r="F120">
-        <v>0.14499999999999999</v>
+        <v>0.58099999999999996</v>
       </c>
     </row>
     <row r="121" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="2" t="s">
+      <c r="A121" t="s">
         <v>11</v>
       </c>
       <c r="B121" t="s">
         <v>7</v>
       </c>
       <c r="C121" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D121">
-        <v>3.4000000000000002E-2</v>
+        <v>0.18</v>
       </c>
       <c r="E121">
-        <v>0.26369999999999999</v>
+        <v>0</v>
       </c>
       <c r="F121">
-        <v>1E-3</v>
+        <v>0.21299999999999999</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B122" t="s">
         <v>14</v>
@@ -3481,318 +3479,318 @@
         <v>22</v>
       </c>
       <c r="D122">
-        <v>0.65800000000000003</v>
+        <v>0.96499999999999997</v>
       </c>
       <c r="E122">
         <v>0</v>
       </c>
       <c r="F122">
-        <v>1.728</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>5.0110000000000001</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B123" t="s">
         <v>14</v>
       </c>
       <c r="C123" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D123">
-        <v>0.42399999999999999</v>
+        <v>0.86199999999999999</v>
       </c>
       <c r="E123">
         <v>0</v>
       </c>
       <c r="F123">
-        <v>1.0089999999999999</v>
+        <v>3.234</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B124" t="s">
         <v>14</v>
       </c>
       <c r="C124" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="D124">
-        <v>0.317</v>
+        <v>0.83099999999999996</v>
       </c>
       <c r="E124">
         <v>0</v>
       </c>
       <c r="F124">
-        <v>0.79100000000000004</v>
+        <v>3.0289999999999999</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B125" t="s">
         <v>14</v>
       </c>
       <c r="C125" t="s">
+        <v>15</v>
+      </c>
+      <c r="D125">
+        <v>0.84899999999999998</v>
+      </c>
+      <c r="E125">
+        <v>0</v>
+      </c>
+      <c r="F125">
+        <v>2.3610000000000002</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B126" t="s">
+        <v>7</v>
+      </c>
+      <c r="C126" t="s">
+        <v>10</v>
+      </c>
+      <c r="D126">
+        <v>5.5E-2</v>
+      </c>
+      <c r="E126">
+        <v>6.1499999999999999E-2</v>
+      </c>
+      <c r="F126">
+        <v>2.9000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A127" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B127" t="s">
+        <v>14</v>
+      </c>
+      <c r="C127" t="s">
+        <v>10</v>
+      </c>
+      <c r="D127">
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="E127">
+        <v>2.7199999999999998E-2</v>
+      </c>
+      <c r="F127">
+        <v>2.4E-2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>18</v>
+      </c>
+      <c r="B128" t="s">
+        <v>7</v>
+      </c>
+      <c r="C128" t="s">
         <v>27</v>
       </c>
-      <c r="D125">
-        <v>0.26100000000000001</v>
-      </c>
-      <c r="E125">
-        <v>0</v>
-      </c>
-      <c r="F125">
-        <v>0.65500000000000003</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" t="s">
-        <v>20</v>
-      </c>
-      <c r="B126" t="s">
-        <v>14</v>
-      </c>
-      <c r="C126" t="s">
+      <c r="D128">
+        <v>0.59</v>
+      </c>
+      <c r="E128">
+        <v>0</v>
+      </c>
+      <c r="F128">
+        <v>1.4970000000000001</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>18</v>
+      </c>
+      <c r="B129" t="s">
+        <v>7</v>
+      </c>
+      <c r="C129" t="s">
+        <v>8</v>
+      </c>
+      <c r="D129">
+        <v>0.59399999999999997</v>
+      </c>
+      <c r="E129">
+        <v>0</v>
+      </c>
+      <c r="F129">
+        <v>1.486</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>18</v>
+      </c>
+      <c r="B130" t="s">
+        <v>7</v>
+      </c>
+      <c r="C130" t="s">
+        <v>15</v>
+      </c>
+      <c r="D130">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="E130">
+        <v>0</v>
+      </c>
+      <c r="F130">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>18</v>
+      </c>
+      <c r="B131" t="s">
+        <v>7</v>
+      </c>
+      <c r="C131" t="s">
         <v>22</v>
       </c>
-      <c r="D126">
-        <v>0.7</v>
-      </c>
-      <c r="E126">
-        <v>0</v>
-      </c>
-      <c r="F126">
-        <v>1.931</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A127" t="s">
-        <v>20</v>
-      </c>
-      <c r="B127" t="s">
-        <v>14</v>
-      </c>
-      <c r="C127" t="s">
-        <v>15</v>
-      </c>
-      <c r="D127">
-        <v>0.58399999999999996</v>
-      </c>
-      <c r="E127">
-        <v>0</v>
-      </c>
-      <c r="F127">
-        <v>1.4650000000000001</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" t="s">
-        <v>20</v>
-      </c>
-      <c r="B128" t="s">
-        <v>14</v>
-      </c>
-      <c r="C128" t="s">
-        <v>8</v>
-      </c>
-      <c r="D128">
-        <v>0.185</v>
-      </c>
-      <c r="E128">
-        <v>0</v>
-      </c>
-      <c r="F128">
-        <v>0.47699999999999998</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B129" t="s">
-        <v>7</v>
-      </c>
-      <c r="C129" t="s">
-        <v>10</v>
-      </c>
-      <c r="D129">
-        <v>5.5E-2</v>
-      </c>
-      <c r="E129">
-        <v>6.1499999999999999E-2</v>
-      </c>
-      <c r="F129">
-        <v>2.9000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" t="s">
-        <v>20</v>
-      </c>
-      <c r="B130" t="s">
-        <v>14</v>
-      </c>
-      <c r="C130" t="s">
-        <v>27</v>
-      </c>
-      <c r="D130">
-        <v>0.193</v>
-      </c>
-      <c r="E130">
-        <v>0</v>
-      </c>
-      <c r="F130">
-        <v>0.44900000000000001</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B131" t="s">
-        <v>14</v>
-      </c>
-      <c r="C131" t="s">
-        <v>10</v>
-      </c>
       <c r="D131">
-        <v>6.0999999999999999E-2</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="E131">
-        <v>2.7199999999999998E-2</v>
+        <v>0</v>
       </c>
       <c r="F131">
-        <v>2.4E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="B132" t="s">
         <v>14</v>
       </c>
       <c r="C132" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D132">
-        <v>0.67600000000000005</v>
+        <v>0.93200000000000005</v>
       </c>
       <c r="E132">
         <v>0</v>
       </c>
       <c r="F132">
-        <v>1.847</v>
+        <v>4.6050000000000004</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="B133" t="s">
         <v>14</v>
       </c>
       <c r="C133" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="D133">
-        <v>0.64</v>
+        <v>0.9</v>
       </c>
       <c r="E133">
         <v>0</v>
       </c>
       <c r="F133">
-        <v>1.7030000000000001</v>
+        <v>3.391</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="B134" t="s">
         <v>14</v>
       </c>
       <c r="C134" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D134">
-        <v>0.59199999999999997</v>
+        <v>0.89600000000000002</v>
       </c>
       <c r="E134">
         <v>0</v>
       </c>
       <c r="F134">
-        <v>1.516</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>2.85</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="B135" t="s">
         <v>14</v>
       </c>
       <c r="C135" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="D135">
-        <v>0.13200000000000001</v>
+        <v>0.78200000000000003</v>
       </c>
       <c r="E135">
         <v>0</v>
       </c>
       <c r="F135">
-        <v>0.1</v>
+        <v>2.6629999999999998</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="B136" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C136" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D136">
-        <v>0.89800000000000002</v>
+        <v>0.127</v>
       </c>
       <c r="E136">
         <v>0</v>
       </c>
       <c r="F136">
-        <v>2.4039999999999999</v>
+        <v>0.33500000000000002</v>
       </c>
     </row>
     <row r="137" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="B137" t="s">
         <v>7</v>
       </c>
       <c r="C137" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D137">
-        <v>0.85599999999999998</v>
+        <v>0.112</v>
       </c>
       <c r="E137">
         <v>0</v>
       </c>
       <c r="F137">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0.21199999999999999</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="B138" t="s">
         <v>7</v>
@@ -3801,18 +3799,18 @@
         <v>27</v>
       </c>
       <c r="D138">
-        <v>0.72199999999999998</v>
+        <v>0.73199999999999998</v>
       </c>
       <c r="E138">
         <v>0</v>
       </c>
       <c r="F138">
-        <v>1.623</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+        <v>2.0209999999999999</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="B139" t="s">
         <v>7</v>
@@ -3821,13 +3819,13 @@
         <v>8</v>
       </c>
       <c r="D139">
-        <v>0.64400000000000002</v>
+        <v>0.749</v>
       </c>
       <c r="E139">
         <v>0</v>
       </c>
       <c r="F139">
-        <v>1.431</v>
+        <v>1.8879999999999999</v>
       </c>
     </row>
     <row r="140" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
@@ -3835,19 +3833,19 @@
         <v>40</v>
       </c>
       <c r="B140" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C140" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D140">
-        <v>0.127</v>
+        <v>0.72199999999999998</v>
       </c>
       <c r="E140">
         <v>0</v>
       </c>
       <c r="F140">
-        <v>0.33500000000000002</v>
+        <v>1.1639999999999999</v>
       </c>
     </row>
     <row r="141" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
@@ -3858,59 +3856,59 @@
         <v>7</v>
       </c>
       <c r="C141" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D141">
-        <v>0.112</v>
+        <v>0.54900000000000004</v>
       </c>
       <c r="E141">
         <v>0</v>
       </c>
       <c r="F141">
-        <v>0.21199999999999999</v>
+        <v>0.90600000000000003</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="B142" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C142" t="s">
+        <v>15</v>
+      </c>
+      <c r="D142">
+        <v>0.52800000000000002</v>
+      </c>
+      <c r="E142">
+        <v>0</v>
+      </c>
+      <c r="F142">
+        <v>1.147</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>6</v>
+      </c>
+      <c r="B143" t="s">
+        <v>14</v>
+      </c>
+      <c r="C143" t="s">
         <v>22</v>
       </c>
-      <c r="D142">
-        <v>0.78</v>
-      </c>
-      <c r="E142">
-        <v>0</v>
-      </c>
-      <c r="F142">
-        <v>1.714</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A143" t="s">
-        <v>30</v>
-      </c>
-      <c r="B143" t="s">
-        <v>7</v>
-      </c>
-      <c r="C143" t="s">
-        <v>15</v>
-      </c>
       <c r="D143">
-        <v>0.73499999999999999</v>
+        <v>0.46600000000000003</v>
       </c>
       <c r="E143">
         <v>0</v>
       </c>
       <c r="F143">
-        <v>1.4610000000000001</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>0.89800000000000002</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>6</v>
       </c>
@@ -3918,236 +3916,236 @@
         <v>14</v>
       </c>
       <c r="C144" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="D144">
-        <v>0.35399999999999998</v>
+        <v>0.27600000000000002</v>
       </c>
       <c r="E144">
         <v>0</v>
       </c>
       <c r="F144">
-        <v>0.877</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>0.58899999999999997</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>6</v>
       </c>
       <c r="B145" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C145" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D145">
-        <v>0.34699999999999998</v>
+        <v>0.161</v>
       </c>
       <c r="E145">
         <v>0</v>
       </c>
       <c r="F145">
-        <v>0.753</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="B146" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C146" t="s">
+        <v>10</v>
+      </c>
+      <c r="D146">
+        <v>0.35399999999999998</v>
+      </c>
+      <c r="E146">
+        <v>0</v>
+      </c>
+      <c r="F146">
+        <v>0.877</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>6</v>
+      </c>
+      <c r="B147" t="s">
+        <v>7</v>
+      </c>
+      <c r="C147" t="s">
+        <v>10</v>
+      </c>
+      <c r="D147">
+        <v>0.34699999999999998</v>
+      </c>
+      <c r="E147">
+        <v>0</v>
+      </c>
+      <c r="F147">
+        <v>0.753</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>6</v>
+      </c>
+      <c r="B148" t="s">
+        <v>7</v>
+      </c>
+      <c r="C148" t="s">
+        <v>27</v>
+      </c>
+      <c r="D148">
+        <v>0.311</v>
+      </c>
+      <c r="E148">
+        <v>0</v>
+      </c>
+      <c r="F148">
+        <v>0.68600000000000005</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>6</v>
+      </c>
+      <c r="B149" t="s">
+        <v>7</v>
+      </c>
+      <c r="C149" t="s">
+        <v>22</v>
+      </c>
+      <c r="D149">
+        <v>0.25900000000000001</v>
+      </c>
+      <c r="E149">
+        <v>0</v>
+      </c>
+      <c r="F149">
+        <v>0.121</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A150" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B150" t="s">
+        <v>7</v>
+      </c>
+      <c r="C150" t="s">
         <v>8</v>
       </c>
-      <c r="D146">
-        <v>0.29699999999999999</v>
-      </c>
-      <c r="E146">
-        <v>0</v>
-      </c>
-      <c r="F146">
-        <v>0.65600000000000003</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A147" t="s">
-        <v>30</v>
-      </c>
-      <c r="B147" t="s">
-        <v>7</v>
-      </c>
-      <c r="C147" t="s">
-        <v>27</v>
-      </c>
-      <c r="D147">
-        <v>0.26900000000000002</v>
-      </c>
-      <c r="E147">
-        <v>0</v>
-      </c>
-      <c r="F147">
-        <v>0.64400000000000002</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A148" t="s">
-        <v>32</v>
-      </c>
-      <c r="B148" t="s">
-        <v>7</v>
-      </c>
-      <c r="C148" t="s">
-        <v>22</v>
-      </c>
-      <c r="D148">
-        <v>0.86699999999999999</v>
-      </c>
-      <c r="E148">
-        <v>0</v>
-      </c>
-      <c r="F148">
-        <v>2.3889999999999998</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A149" t="s">
-        <v>32</v>
-      </c>
-      <c r="B149" t="s">
-        <v>7</v>
-      </c>
-      <c r="C149" t="s">
-        <v>8</v>
-      </c>
-      <c r="D149">
-        <v>0.76100000000000001</v>
-      </c>
-      <c r="E149">
-        <v>0</v>
-      </c>
-      <c r="F149">
-        <v>1.92</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A150" t="s">
-        <v>32</v>
-      </c>
-      <c r="B150" t="s">
-        <v>7</v>
-      </c>
-      <c r="C150" t="s">
+      <c r="D150">
+        <v>4.7E-2</v>
+      </c>
+      <c r="E150">
+        <v>0.36149999999999999</v>
+      </c>
+      <c r="F150">
+        <v>8.8999999999999996E-2</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>6</v>
+      </c>
+      <c r="B151" t="s">
+        <v>7</v>
+      </c>
+      <c r="C151" t="s">
         <v>15</v>
       </c>
-      <c r="D150">
-        <v>0.81799999999999995</v>
-      </c>
-      <c r="E150">
-        <v>0</v>
-      </c>
-      <c r="F150">
-        <v>1.702</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A151" t="s">
-        <v>32</v>
-      </c>
-      <c r="B151" t="s">
-        <v>7</v>
-      </c>
-      <c r="C151" t="s">
-        <v>27</v>
-      </c>
       <c r="D151">
-        <v>0.58199999999999996</v>
+        <v>0.27</v>
       </c>
       <c r="E151">
         <v>0</v>
       </c>
       <c r="F151">
-        <v>1.3520000000000001</v>
+        <v>7.9000000000000001E-2</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B152" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C152" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D152">
-        <v>0.86899999999999999</v>
+        <v>0.443</v>
       </c>
       <c r="E152">
         <v>0</v>
       </c>
       <c r="F152">
-        <v>2.3410000000000002</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>1.0720000000000001</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B153" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C153" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D153">
-        <v>0.81399999999999995</v>
+        <v>0.24199999999999999</v>
       </c>
       <c r="E153">
         <v>0</v>
       </c>
       <c r="F153">
-        <v>1.9490000000000001</v>
+        <v>0.47499999999999998</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B154" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C154" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D154">
-        <v>0.46400000000000002</v>
+        <v>0.112</v>
       </c>
       <c r="E154">
-        <v>0</v>
+        <v>1E-4</v>
       </c>
       <c r="F154">
-        <v>1.234</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>0.23699999999999999</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>28</v>
       </c>
       <c r="B155" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C155" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D155">
-        <v>0.27100000000000002</v>
+        <v>0.189</v>
       </c>
       <c r="E155">
         <v>0</v>
       </c>
       <c r="F155">
-        <v>0.623</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="156" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
@@ -4155,239 +4153,239 @@
         <v>28</v>
       </c>
       <c r="B156" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C156" t="s">
         <v>10</v>
       </c>
       <c r="D156">
-        <v>0.25900000000000001</v>
+        <v>0.27100000000000002</v>
       </c>
       <c r="E156">
         <v>0</v>
       </c>
       <c r="F156">
-        <v>0.57999999999999996</v>
+        <v>0.623</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B157" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C157" t="s">
+        <v>10</v>
+      </c>
+      <c r="D157">
+        <v>0.25900000000000001</v>
+      </c>
+      <c r="E157">
+        <v>0</v>
+      </c>
+      <c r="F157">
+        <v>0.57999999999999996</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>28</v>
+      </c>
+      <c r="B158" t="s">
+        <v>7</v>
+      </c>
+      <c r="C158" t="s">
+        <v>27</v>
+      </c>
+      <c r="D158">
+        <v>0.48199999999999998</v>
+      </c>
+      <c r="E158">
+        <v>0</v>
+      </c>
+      <c r="F158">
+        <v>1.2490000000000001</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>28</v>
+      </c>
+      <c r="B159" t="s">
+        <v>7</v>
+      </c>
+      <c r="C159" t="s">
         <v>8</v>
       </c>
-      <c r="D157">
-        <v>0.29199999999999998</v>
-      </c>
-      <c r="E157">
-        <v>0</v>
-      </c>
-      <c r="F157">
-        <v>0.49299999999999999</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A158" t="s">
-        <v>37</v>
-      </c>
-      <c r="B158" t="s">
-        <v>7</v>
-      </c>
-      <c r="C158" t="s">
-        <v>22</v>
-      </c>
-      <c r="D158">
-        <v>0.67300000000000004</v>
-      </c>
-      <c r="E158">
-        <v>0</v>
-      </c>
-      <c r="F158">
-        <v>1.45</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A159" t="s">
-        <v>37</v>
-      </c>
-      <c r="B159" t="s">
-        <v>7</v>
-      </c>
-      <c r="C159" t="s">
-        <v>27</v>
-      </c>
       <c r="D159">
-        <v>0.60199999999999998</v>
+        <v>0.28599999999999998</v>
       </c>
       <c r="E159">
         <v>0</v>
       </c>
       <c r="F159">
-        <v>1.431</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0.68799999999999994</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B160" t="s">
         <v>7</v>
       </c>
       <c r="C160" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D160">
-        <v>0.51600000000000001</v>
+        <v>0.19600000000000001</v>
       </c>
       <c r="E160">
         <v>0</v>
       </c>
       <c r="F160">
-        <v>1.161</v>
+        <v>0.46600000000000003</v>
       </c>
     </row>
     <row r="161" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B161" t="s">
         <v>7</v>
       </c>
       <c r="C161" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D161">
-        <v>0.53800000000000003</v>
+        <v>0.14599999999999999</v>
       </c>
       <c r="E161">
         <v>0</v>
       </c>
       <c r="F161">
-        <v>0.88600000000000001</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B162" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C162" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D162">
-        <v>0.93400000000000005</v>
+        <v>0.76</v>
       </c>
       <c r="E162">
         <v>0</v>
       </c>
       <c r="F162">
-        <v>3.0379999999999998</v>
+        <v>2.1720000000000002</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B163" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C163" t="s">
+        <v>15</v>
+      </c>
+      <c r="D163">
+        <v>0.49399999999999999</v>
+      </c>
+      <c r="E163">
+        <v>0</v>
+      </c>
+      <c r="F163">
+        <v>1.292</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>31</v>
+      </c>
+      <c r="B164" t="s">
+        <v>14</v>
+      </c>
+      <c r="C164" t="s">
         <v>8</v>
       </c>
-      <c r="D163">
-        <v>0.78500000000000003</v>
-      </c>
-      <c r="E163">
-        <v>0</v>
-      </c>
-      <c r="F163">
-        <v>2.2309999999999999</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A164" t="s">
-        <v>38</v>
-      </c>
-      <c r="B164" t="s">
-        <v>7</v>
-      </c>
-      <c r="C164" t="s">
-        <v>15</v>
-      </c>
       <c r="D164">
-        <v>0.47499999999999998</v>
+        <v>0.32</v>
       </c>
       <c r="E164">
         <v>0</v>
       </c>
       <c r="F164">
-        <v>1.0109999999999999</v>
+        <v>0.63200000000000001</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B165" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C165" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D165">
-        <v>0.45900000000000002</v>
+        <v>0.14499999999999999</v>
       </c>
       <c r="E165">
         <v>0</v>
       </c>
       <c r="F165">
-        <v>0.96199999999999997</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0.29699999999999999</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B166" t="s">
         <v>7</v>
       </c>
       <c r="C166" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D166">
-        <v>0.86299999999999999</v>
+        <v>0.19400000000000001</v>
       </c>
       <c r="E166">
         <v>0</v>
       </c>
       <c r="F166">
-        <v>3.0390000000000001</v>
+        <v>0.38200000000000001</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B167" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C167" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="D167">
-        <v>0.83799999999999997</v>
+        <v>0.214</v>
       </c>
       <c r="E167">
         <v>0</v>
       </c>
       <c r="F167">
-        <v>3.0089999999999999</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="168" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
@@ -4398,16 +4396,16 @@
         <v>7</v>
       </c>
       <c r="C168" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D168">
-        <v>0.19400000000000001</v>
+        <v>0.626</v>
       </c>
       <c r="E168">
         <v>0</v>
       </c>
       <c r="F168">
-        <v>0.38200000000000001</v>
+        <v>1.137</v>
       </c>
     </row>
     <row r="169" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
@@ -4415,219 +4413,219 @@
         <v>31</v>
       </c>
       <c r="B169" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C169" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D169">
-        <v>0.214</v>
+        <v>0.39900000000000002</v>
       </c>
       <c r="E169">
         <v>0</v>
       </c>
       <c r="F169">
-        <v>0.38</v>
+        <v>0.69699999999999995</v>
       </c>
     </row>
     <row r="170" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B170" t="s">
         <v>7</v>
       </c>
       <c r="C170" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D170">
-        <v>0.85299999999999998</v>
+        <v>0.27700000000000002</v>
       </c>
       <c r="E170">
         <v>0</v>
       </c>
       <c r="F170">
-        <v>2.64</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0.59499999999999997</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B171" t="s">
         <v>7</v>
       </c>
       <c r="C171" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D171">
-        <v>0.52100000000000002</v>
+        <v>0.151</v>
       </c>
       <c r="E171">
         <v>0</v>
       </c>
       <c r="F171">
-        <v>0.79900000000000004</v>
+        <v>0.28000000000000003</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B172" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C172" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D172">
-        <v>0.85099999999999998</v>
+        <v>0.747</v>
       </c>
       <c r="E172">
         <v>0</v>
       </c>
       <c r="F172">
-        <v>1.367</v>
+        <v>2.1850000000000001</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B173" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C173" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D173">
-        <v>0.86899999999999999</v>
+        <v>0.64900000000000002</v>
       </c>
       <c r="E173">
         <v>0</v>
       </c>
       <c r="F173">
-        <v>1.365</v>
+        <v>1.7170000000000001</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B174" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C174" t="s">
         <v>8</v>
       </c>
       <c r="D174">
-        <v>0.85099999999999998</v>
+        <v>0.245</v>
       </c>
       <c r="E174">
         <v>0</v>
       </c>
       <c r="F174">
-        <v>1.361</v>
-      </c>
-    </row>
-    <row r="175" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A175" s="2" t="s">
-        <v>9</v>
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>17</v>
       </c>
       <c r="B175" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C175" t="s">
+        <v>27</v>
+      </c>
+      <c r="D175">
+        <v>0.214</v>
+      </c>
+      <c r="E175">
+        <v>0</v>
+      </c>
+      <c r="F175">
+        <v>0.46899999999999997</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>17</v>
+      </c>
+      <c r="B176" t="s">
+        <v>7</v>
+      </c>
+      <c r="C176" t="s">
+        <v>10</v>
+      </c>
+      <c r="D176">
+        <v>8.7999999999999995E-2</v>
+      </c>
+      <c r="E176">
+        <v>0</v>
+      </c>
+      <c r="F176">
+        <v>0.154</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A177" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B177" t="s">
+        <v>14</v>
+      </c>
+      <c r="C177" t="s">
+        <v>10</v>
+      </c>
+      <c r="D177">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="E177">
+        <v>8.5900000000000004E-2</v>
+      </c>
+      <c r="F177">
+        <v>5.7000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>17</v>
+      </c>
+      <c r="B178" t="s">
+        <v>7</v>
+      </c>
+      <c r="C178" t="s">
         <v>15</v>
       </c>
-      <c r="D175">
-        <v>4.2000000000000003E-2</v>
-      </c>
-      <c r="E175">
-        <v>9.8199999999999996E-2</v>
-      </c>
-      <c r="F175">
-        <v>4.5999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A176" t="s">
-        <v>19</v>
-      </c>
-      <c r="B176" t="s">
-        <v>7</v>
-      </c>
-      <c r="C176" t="s">
+      <c r="D178">
+        <v>0.64</v>
+      </c>
+      <c r="E178">
+        <v>0</v>
+      </c>
+      <c r="F178">
+        <v>1.046</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>17</v>
+      </c>
+      <c r="B179" t="s">
+        <v>7</v>
+      </c>
+      <c r="C179" t="s">
         <v>22</v>
       </c>
-      <c r="D176">
-        <v>0.20799999999999999</v>
-      </c>
-      <c r="E176">
-        <v>0</v>
-      </c>
-      <c r="F176">
-        <v>0.20200000000000001</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A177" t="s">
-        <v>19</v>
-      </c>
-      <c r="B177" t="s">
-        <v>7</v>
-      </c>
-      <c r="C177" t="s">
-        <v>8</v>
-      </c>
-      <c r="D177">
-        <v>0.23400000000000001</v>
-      </c>
-      <c r="E177">
-        <v>0</v>
-      </c>
-      <c r="F177">
-        <v>0.182</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A178" t="s">
-        <v>19</v>
-      </c>
-      <c r="B178" t="s">
-        <v>7</v>
-      </c>
-      <c r="C178" t="s">
-        <v>27</v>
-      </c>
-      <c r="D178">
-        <v>0.23400000000000001</v>
-      </c>
-      <c r="E178">
-        <v>0</v>
-      </c>
-      <c r="F178">
-        <v>0.14399999999999999</v>
-      </c>
-    </row>
-    <row r="179" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A179" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B179" t="s">
-        <v>7</v>
-      </c>
-      <c r="C179" t="s">
-        <v>15</v>
-      </c>
       <c r="D179">
-        <v>4.4999999999999998E-2</v>
+        <v>0.55200000000000005</v>
       </c>
       <c r="E179">
-        <v>5.8200000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="F179">
-        <v>4.4999999999999998E-2</v>
+        <v>0.82499999999999996</v>
       </c>
     </row>
     <row r="180" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
@@ -4638,279 +4636,279 @@
         <v>7</v>
       </c>
       <c r="C180" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D180">
-        <v>8.7999999999999995E-2</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="E180">
         <v>0</v>
       </c>
       <c r="F180">
-        <v>0.154</v>
+        <v>0.54600000000000004</v>
       </c>
     </row>
     <row r="181" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A181" s="2" t="s">
+      <c r="A181" t="s">
         <v>17</v>
       </c>
       <c r="B181" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C181" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="D181">
-        <v>4.2999999999999997E-2</v>
+        <v>0.189</v>
       </c>
       <c r="E181">
-        <v>8.5900000000000004E-2</v>
+        <v>0</v>
       </c>
       <c r="F181">
-        <v>5.7000000000000002E-2</v>
+        <v>0.42799999999999999</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B182" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C182" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="D182">
-        <v>0.38700000000000001</v>
+        <v>0.58899999999999997</v>
       </c>
       <c r="E182">
         <v>0</v>
       </c>
       <c r="F182">
-        <v>0.27</v>
+        <v>1.5069999999999999</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B183" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C183" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="D183">
-        <v>0.377</v>
+        <v>0.54800000000000004</v>
       </c>
       <c r="E183">
         <v>0</v>
       </c>
       <c r="F183">
-        <v>0.25900000000000001</v>
+        <v>1.4019999999999999</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B184" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C184" t="s">
+        <v>15</v>
+      </c>
+      <c r="D184">
+        <v>0.32300000000000001</v>
+      </c>
+      <c r="E184">
+        <v>0</v>
+      </c>
+      <c r="F184">
+        <v>0.83299999999999996</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>12</v>
+      </c>
+      <c r="B185" t="s">
+        <v>14</v>
+      </c>
+      <c r="C185" t="s">
         <v>22</v>
       </c>
-      <c r="D184">
-        <v>0.34699999999999998</v>
-      </c>
-      <c r="E184">
-        <v>0</v>
-      </c>
-      <c r="F184">
-        <v>0.22800000000000001</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A185" t="s">
-        <v>13</v>
-      </c>
-      <c r="B185" t="s">
-        <v>7</v>
-      </c>
-      <c r="C185" t="s">
-        <v>15</v>
-      </c>
       <c r="D185">
-        <v>6.8000000000000005E-2</v>
+        <v>0.28699999999999998</v>
       </c>
       <c r="E185">
-        <v>6.9999999999999999E-4</v>
+        <v>0</v>
       </c>
       <c r="F185">
-        <v>8.5999999999999993E-2</v>
+        <v>0.55700000000000005</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A186" t="s">
-        <v>39</v>
+      <c r="A186" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="B186" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C186" t="s">
+        <v>10</v>
+      </c>
+      <c r="D186">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="E186">
+        <v>9.9500000000000005E-2</v>
+      </c>
+      <c r="F186">
+        <v>7.5999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A187" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B187" t="s">
+        <v>7</v>
+      </c>
+      <c r="C187" t="s">
+        <v>10</v>
+      </c>
+      <c r="D187">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="E187">
+        <v>0.252</v>
+      </c>
+      <c r="F187">
+        <v>1.7999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>12</v>
+      </c>
+      <c r="B188" t="s">
+        <v>7</v>
+      </c>
+      <c r="C188" t="s">
         <v>8</v>
       </c>
-      <c r="D186">
-        <v>0.377</v>
-      </c>
-      <c r="E186">
-        <v>0</v>
-      </c>
-      <c r="F186">
-        <v>0.29599999999999999</v>
-      </c>
-    </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A187" t="s">
-        <v>39</v>
-      </c>
-      <c r="B187" t="s">
-        <v>7</v>
-      </c>
-      <c r="C187" t="s">
-        <v>27</v>
-      </c>
-      <c r="D187">
-        <v>0.36599999999999999</v>
-      </c>
-      <c r="E187">
-        <v>0</v>
-      </c>
-      <c r="F187">
-        <v>0.22500000000000001</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A188" t="s">
-        <v>39</v>
-      </c>
-      <c r="B188" t="s">
-        <v>7</v>
-      </c>
-      <c r="C188" t="s">
-        <v>22</v>
-      </c>
       <c r="D188">
-        <v>0.317</v>
+        <v>0.624</v>
       </c>
       <c r="E188">
         <v>0</v>
       </c>
       <c r="F188">
-        <v>0.224</v>
+        <v>1.5580000000000001</v>
       </c>
     </row>
     <row r="189" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="B189" t="s">
         <v>7</v>
       </c>
       <c r="C189" t="s">
+        <v>27</v>
+      </c>
+      <c r="D189">
+        <v>0.59299999999999997</v>
+      </c>
+      <c r="E189">
+        <v>0</v>
+      </c>
+      <c r="F189">
+        <v>1.359</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>12</v>
+      </c>
+      <c r="B190" t="s">
+        <v>7</v>
+      </c>
+      <c r="C190" t="s">
+        <v>22</v>
+      </c>
+      <c r="D190">
+        <v>0.443</v>
+      </c>
+      <c r="E190">
+        <v>0</v>
+      </c>
+      <c r="F190">
+        <v>0.81899999999999995</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>12</v>
+      </c>
+      <c r="B191" t="s">
+        <v>7</v>
+      </c>
+      <c r="C191" t="s">
         <v>15</v>
       </c>
-      <c r="D189">
-        <v>0.10199999999999999</v>
-      </c>
-      <c r="E189">
-        <v>0</v>
-      </c>
-      <c r="F189">
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="190" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B190" t="s">
-        <v>14</v>
-      </c>
-      <c r="C190" t="s">
-        <v>10</v>
-      </c>
-      <c r="D190">
-        <v>5.0999999999999997E-2</v>
-      </c>
-      <c r="E190">
-        <v>9.9500000000000005E-2</v>
-      </c>
-      <c r="F190">
-        <v>7.5999999999999998E-2</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A191" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B191" t="s">
-        <v>7</v>
-      </c>
-      <c r="C191" t="s">
-        <v>10</v>
-      </c>
       <c r="D191">
-        <v>4.2000000000000003E-2</v>
+        <v>0.20699999999999999</v>
       </c>
       <c r="E191">
-        <v>0.252</v>
+        <v>0</v>
       </c>
       <c r="F191">
-        <v>1.7999999999999999E-2</v>
+        <v>0.161</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="B192" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C192" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D192">
-        <v>0.621</v>
+        <v>0.629</v>
       </c>
       <c r="E192">
         <v>0</v>
       </c>
       <c r="F192">
-        <v>0.66200000000000003</v>
+        <v>1.6579999999999999</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="B193" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C193" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="D193">
-        <v>0.624</v>
+        <v>0.55100000000000005</v>
       </c>
       <c r="E193">
         <v>0</v>
       </c>
       <c r="F193">
-        <v>0.65800000000000003</v>
-      </c>
-    </row>
-    <row r="194" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>1.286</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>34</v>
       </c>
@@ -4918,81 +4916,81 @@
         <v>14</v>
       </c>
       <c r="C194" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="D194">
-        <v>0.39900000000000002</v>
+        <v>0.247</v>
       </c>
       <c r="E194">
         <v>0</v>
       </c>
       <c r="F194">
-        <v>0.95099999999999996</v>
-      </c>
-    </row>
-    <row r="195" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>0.56899999999999995</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>34</v>
       </c>
       <c r="B195" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C195" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D195">
-        <v>0.42799999999999999</v>
+        <v>0.193</v>
       </c>
       <c r="E195">
         <v>0</v>
       </c>
       <c r="F195">
-        <v>0.89</v>
+        <v>0.39700000000000002</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="B196" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C196" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D196">
-        <v>0.52900000000000003</v>
+        <v>0.39900000000000002</v>
       </c>
       <c r="E196">
         <v>0</v>
       </c>
       <c r="F196">
-        <v>0.58099999999999996</v>
+        <v>0.95099999999999996</v>
       </c>
     </row>
     <row r="197" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="B197" t="s">
         <v>7</v>
       </c>
       <c r="C197" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D197">
-        <v>0.18</v>
+        <v>0.42799999999999999</v>
       </c>
       <c r="E197">
         <v>0</v>
       </c>
       <c r="F197">
-        <v>0.21299999999999999</v>
-      </c>
-    </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="B198" t="s">
         <v>7</v>
@@ -5001,233 +4999,233 @@
         <v>27</v>
       </c>
       <c r="D198">
-        <v>0.59</v>
+        <v>0.28399999999999997</v>
       </c>
       <c r="E198">
         <v>0</v>
       </c>
       <c r="F198">
-        <v>1.4970000000000001</v>
-      </c>
-    </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0.60299999999999998</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="B199" t="s">
         <v>7</v>
       </c>
       <c r="C199" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D199">
-        <v>0.59399999999999997</v>
+        <v>0.49</v>
       </c>
       <c r="E199">
         <v>0</v>
       </c>
       <c r="F199">
-        <v>1.486</v>
+        <v>0.48199999999999998</v>
       </c>
     </row>
     <row r="200" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="B200" t="s">
         <v>7</v>
       </c>
       <c r="C200" t="s">
+        <v>8</v>
+      </c>
+      <c r="D200">
+        <v>0.17799999999999999</v>
+      </c>
+      <c r="E200">
+        <v>0</v>
+      </c>
+      <c r="F200">
+        <v>0.36399999999999999</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
+        <v>34</v>
+      </c>
+      <c r="B201" t="s">
+        <v>7</v>
+      </c>
+      <c r="C201" t="s">
         <v>15</v>
       </c>
-      <c r="D200">
-        <v>0.56499999999999995</v>
-      </c>
-      <c r="E200">
-        <v>0</v>
-      </c>
-      <c r="F200">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A201" t="s">
-        <v>18</v>
-      </c>
-      <c r="B201" t="s">
-        <v>7</v>
-      </c>
-      <c r="C201" t="s">
-        <v>22</v>
-      </c>
       <c r="D201">
-        <v>0.28499999999999998</v>
+        <v>0.41699999999999998</v>
       </c>
       <c r="E201">
         <v>0</v>
       </c>
       <c r="F201">
-        <v>2.5000000000000001E-2</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="B202" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C202" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="D202">
-        <v>0.73199999999999998</v>
+        <v>0.81599999999999995</v>
       </c>
       <c r="E202">
         <v>0</v>
       </c>
       <c r="F202">
-        <v>2.0209999999999999</v>
+        <v>2.2869999999999999</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="B203" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C203" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D203">
-        <v>0.749</v>
+        <v>0.64100000000000001</v>
       </c>
       <c r="E203">
         <v>0</v>
       </c>
       <c r="F203">
-        <v>1.8879999999999999</v>
-      </c>
-    </row>
-    <row r="204" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>1.7110000000000001</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="B204" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C204" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="D204">
-        <v>0.72199999999999998</v>
+        <v>0.375</v>
       </c>
       <c r="E204">
         <v>0</v>
       </c>
       <c r="F204">
-        <v>1.1639999999999999</v>
+        <v>0.90300000000000002</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="B205" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C205" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D205">
-        <v>0.54900000000000004</v>
+        <v>0.33500000000000002</v>
       </c>
       <c r="E205">
         <v>0</v>
       </c>
       <c r="F205">
-        <v>0.90600000000000003</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="B206" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C206" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="D206">
-        <v>0.311</v>
+        <v>0.08</v>
       </c>
       <c r="E206">
-        <v>0</v>
+        <v>1.1999999999999999E-3</v>
       </c>
       <c r="F206">
-        <v>0.68600000000000005</v>
-      </c>
-    </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0.122</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="B207" t="s">
         <v>7</v>
       </c>
       <c r="C207" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D207">
-        <v>0.25900000000000001</v>
+        <v>8.4000000000000005E-2</v>
       </c>
       <c r="E207">
-        <v>0</v>
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="F207">
-        <v>0.121</v>
-      </c>
-    </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A208" s="2" t="s">
-        <v>6</v>
+        <v>5.8999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
+        <v>26</v>
       </c>
       <c r="B208" t="s">
         <v>7</v>
       </c>
       <c r="C208" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D208">
-        <v>4.7E-2</v>
+        <v>0.82599999999999996</v>
       </c>
       <c r="E208">
-        <v>0.36149999999999999</v>
+        <v>0</v>
       </c>
       <c r="F208">
-        <v>8.8999999999999996E-2</v>
+        <v>2.0990000000000002</v>
       </c>
     </row>
     <row r="209" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="B209" t="s">
         <v>7</v>
       </c>
       <c r="C209" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D209">
-        <v>0.27</v>
+        <v>0.65900000000000003</v>
       </c>
       <c r="E209">
         <v>0</v>
       </c>
       <c r="F209">
-        <v>7.9000000000000001E-2</v>
+        <v>1.6870000000000001</v>
       </c>
     </row>
     <row r="210" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
@@ -5235,19 +5233,19 @@
         <v>26</v>
       </c>
       <c r="B210" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C210" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D210">
-        <v>0.08</v>
+        <v>0.35499999999999998</v>
       </c>
       <c r="E210">
-        <v>1.1999999999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="F210">
-        <v>0.122</v>
+        <v>0.74399999999999999</v>
       </c>
     </row>
     <row r="211" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
@@ -5258,136 +5256,136 @@
         <v>7</v>
       </c>
       <c r="C211" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="D211">
-        <v>8.4000000000000005E-2</v>
+        <v>0.42099999999999999</v>
       </c>
       <c r="E211">
-        <v>5.9999999999999995E-4</v>
+        <v>0</v>
       </c>
       <c r="F211">
-        <v>5.8999999999999997E-2</v>
+        <v>0.63700000000000001</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B212" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C212" t="s">
         <v>27</v>
       </c>
       <c r="D212">
-        <v>0.48199999999999998</v>
+        <v>0.66600000000000004</v>
       </c>
       <c r="E212">
         <v>0</v>
       </c>
       <c r="F212">
-        <v>1.2490000000000001</v>
+        <v>1.833</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B213" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C213" t="s">
         <v>8</v>
       </c>
       <c r="D213">
-        <v>0.28599999999999998</v>
+        <v>0.59699999999999998</v>
       </c>
       <c r="E213">
         <v>0</v>
       </c>
       <c r="F213">
-        <v>0.68799999999999994</v>
-      </c>
-    </row>
-    <row r="214" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>1.4970000000000001</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B214" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C214" t="s">
         <v>15</v>
       </c>
       <c r="D214">
-        <v>0.19600000000000001</v>
+        <v>0.52200000000000002</v>
       </c>
       <c r="E214">
         <v>0</v>
       </c>
       <c r="F214">
-        <v>0.46600000000000003</v>
+        <v>1.2869999999999999</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B215" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C215" t="s">
         <v>22</v>
       </c>
       <c r="D215">
-        <v>0.14599999999999999</v>
+        <v>0.153</v>
       </c>
       <c r="E215">
         <v>0</v>
       </c>
       <c r="F215">
-        <v>0.21</v>
+        <v>7.0999999999999994E-2</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B216" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C216" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D216">
-        <v>0.626</v>
+        <v>0.20100000000000001</v>
       </c>
       <c r="E216">
         <v>0</v>
       </c>
       <c r="F216">
-        <v>1.137</v>
+        <v>0.42599999999999999</v>
       </c>
     </row>
     <row r="217" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B217" t="s">
         <v>7</v>
       </c>
       <c r="C217" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D217">
-        <v>0.39900000000000002</v>
+        <v>0.157</v>
       </c>
       <c r="E217">
         <v>0</v>
       </c>
       <c r="F217">
-        <v>0.69699999999999995</v>
+        <v>0.29699999999999999</v>
       </c>
     </row>
     <row r="218" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
@@ -5395,19 +5393,19 @@
         <v>33</v>
       </c>
       <c r="B218" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C218" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="D218">
-        <v>0.20100000000000001</v>
+        <v>0.754</v>
       </c>
       <c r="E218">
         <v>0</v>
       </c>
       <c r="F218">
-        <v>0.42599999999999999</v>
+        <v>1.9019999999999999</v>
       </c>
     </row>
     <row r="219" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
@@ -5418,259 +5416,259 @@
         <v>7</v>
       </c>
       <c r="C219" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D219">
-        <v>0.157</v>
+        <v>0.69</v>
       </c>
       <c r="E219">
         <v>0</v>
       </c>
       <c r="F219">
-        <v>0.29699999999999999</v>
-      </c>
-    </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1.6850000000000001</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B220" t="s">
         <v>7</v>
       </c>
       <c r="C220" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D220">
-        <v>0.27700000000000002</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="E220">
         <v>0</v>
       </c>
       <c r="F220">
-        <v>0.59499999999999997</v>
-      </c>
-    </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1.304</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B221" t="s">
         <v>7</v>
       </c>
       <c r="C221" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D221">
-        <v>0.151</v>
+        <v>0.153</v>
       </c>
       <c r="E221">
         <v>0</v>
       </c>
       <c r="F221">
-        <v>0.28000000000000003</v>
-      </c>
-    </row>
-    <row r="222" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>0.122</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B222" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C222" t="s">
         <v>15</v>
       </c>
       <c r="D222">
-        <v>0.64</v>
+        <v>0.29699999999999999</v>
       </c>
       <c r="E222">
         <v>0</v>
       </c>
       <c r="F222">
-        <v>1.046</v>
+        <v>0.61699999999999999</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B223" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C223" t="s">
         <v>22</v>
       </c>
       <c r="D223">
-        <v>0.55200000000000005</v>
+        <v>0.26200000000000001</v>
       </c>
       <c r="E223">
         <v>0</v>
       </c>
       <c r="F223">
-        <v>0.82499999999999996</v>
+        <v>0.44500000000000001</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B224" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C224" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="D224">
-        <v>0.26400000000000001</v>
+        <v>0.113</v>
       </c>
       <c r="E224">
         <v>0</v>
       </c>
       <c r="F224">
-        <v>0.54600000000000004</v>
+        <v>0.214</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B225" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C225" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="D225">
-        <v>0.189</v>
+        <v>7.5999999999999998E-2</v>
       </c>
       <c r="E225">
-        <v>0</v>
+        <v>3.0999999999999999E-3</v>
       </c>
       <c r="F225">
-        <v>0.42799999999999999</v>
-      </c>
-    </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A226" t="s">
-        <v>12</v>
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A226" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="B226" t="s">
         <v>7</v>
       </c>
       <c r="C226" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D226">
-        <v>0.624</v>
+        <v>6.7000000000000004E-2</v>
       </c>
       <c r="E226">
-        <v>0</v>
+        <v>1.32E-2</v>
       </c>
       <c r="F226">
-        <v>1.5580000000000001</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A227" t="s">
-        <v>12</v>
+      <c r="A227" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="B227" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C227" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="D227">
-        <v>0.59299999999999997</v>
+        <v>5.2999999999999999E-2</v>
       </c>
       <c r="E227">
-        <v>0</v>
+        <v>8.9399999999999993E-2</v>
       </c>
       <c r="F227">
-        <v>1.359</v>
-      </c>
-    </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
+        <v>2.3E-2</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B228" t="s">
         <v>7</v>
       </c>
       <c r="C228" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D228">
-        <v>0.443</v>
+        <v>0.312</v>
       </c>
       <c r="E228">
         <v>0</v>
       </c>
       <c r="F228">
-        <v>0.81899999999999995</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="229" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B229" t="s">
         <v>7</v>
       </c>
       <c r="C229" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D229">
-        <v>0.20699999999999999</v>
+        <v>0.246</v>
       </c>
       <c r="E229">
         <v>0</v>
       </c>
       <c r="F229">
-        <v>0.161</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="230" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A230" s="2" t="s">
+      <c r="A230" t="s">
         <v>16</v>
       </c>
       <c r="B230" t="s">
         <v>7</v>
       </c>
       <c r="C230" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="D230">
-        <v>6.7000000000000004E-2</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="E230">
-        <v>1.32E-2</v>
+        <v>0</v>
       </c>
       <c r="F230">
-        <v>0.05</v>
+        <v>0.32100000000000001</v>
       </c>
     </row>
     <row r="231" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A231" s="2" t="s">
+      <c r="A231" t="s">
         <v>16</v>
       </c>
       <c r="B231" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C231" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D231">
-        <v>5.2999999999999999E-2</v>
+        <v>0.122</v>
       </c>
       <c r="E231">
-        <v>8.9399999999999993E-2</v>
+        <v>0</v>
       </c>
       <c r="F231">
-        <v>2.3E-2</v>
-      </c>
-    </row>
-    <row r="232" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>0.27800000000000002</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>21</v>
       </c>
@@ -5678,141 +5676,141 @@
         <v>14</v>
       </c>
       <c r="C232" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D232">
-        <v>0.13800000000000001</v>
+        <v>0.10199999999999999</v>
       </c>
       <c r="E232">
         <v>0</v>
       </c>
       <c r="F232">
-        <v>0.22700000000000001</v>
+        <v>0.17899999999999999</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="B233" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C233" t="s">
         <v>27</v>
       </c>
       <c r="D233">
-        <v>0.28399999999999997</v>
+        <v>0.105</v>
       </c>
       <c r="E233">
         <v>0</v>
       </c>
       <c r="F233">
-        <v>0.60299999999999998</v>
+        <v>0.17499999999999999</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A234" t="s">
-        <v>34</v>
+      <c r="A234" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="B234" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C234" t="s">
         <v>22</v>
       </c>
       <c r="D234">
-        <v>0.49</v>
+        <v>6.3E-2</v>
       </c>
       <c r="E234">
-        <v>0</v>
+        <v>2.2200000000000001E-2</v>
       </c>
       <c r="F234">
-        <v>0.48199999999999998</v>
+        <v>0.121</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="B235" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C235" t="s">
         <v>8</v>
       </c>
       <c r="D235">
-        <v>0.17799999999999999</v>
+        <v>8.3000000000000004E-2</v>
       </c>
       <c r="E235">
-        <v>0</v>
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="F235">
-        <v>0.36399999999999999</v>
-      </c>
-    </row>
-    <row r="236" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>7.3999999999999996E-2</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>21</v>
       </c>
       <c r="B236" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C236" t="s">
         <v>10</v>
       </c>
       <c r="D236">
-        <v>0.14599999999999999</v>
+        <v>0.13800000000000001</v>
       </c>
       <c r="E236">
         <v>0</v>
       </c>
       <c r="F236">
-        <v>0.16700000000000001</v>
+        <v>0.22700000000000001</v>
       </c>
     </row>
     <row r="237" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="B237" t="s">
         <v>7</v>
       </c>
       <c r="C237" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D237">
-        <v>0.41699999999999998</v>
+        <v>0.14599999999999999</v>
       </c>
       <c r="E237">
         <v>0</v>
       </c>
       <c r="F237">
-        <v>0.31</v>
+        <v>0.16700000000000001</v>
       </c>
     </row>
     <row r="238" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B238" t="s">
         <v>7</v>
       </c>
       <c r="C238" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="D238">
-        <v>0.82599999999999996</v>
+        <v>9.1999999999999998E-2</v>
       </c>
       <c r="E238">
-        <v>0</v>
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="F238">
-        <v>2.0990000000000002</v>
-      </c>
-    </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A239" t="s">
-        <v>26</v>
+        <v>0.19700000000000001</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A239" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="B239" t="s">
         <v>7</v>
@@ -5821,213 +5819,213 @@
         <v>22</v>
       </c>
       <c r="D239">
-        <v>0.65900000000000003</v>
+        <v>6.4000000000000001E-2</v>
       </c>
       <c r="E239">
-        <v>0</v>
+        <v>1.95E-2</v>
       </c>
       <c r="F239">
-        <v>1.6870000000000001</v>
-      </c>
-    </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0.14899999999999999</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B240" t="s">
         <v>7</v>
       </c>
       <c r="C240" t="s">
+        <v>15</v>
+      </c>
+      <c r="D240">
+        <v>0.126</v>
+      </c>
+      <c r="E240">
+        <v>0</v>
+      </c>
+      <c r="F240">
+        <v>0.123</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A241" t="s">
+        <v>21</v>
+      </c>
+      <c r="B241" t="s">
+        <v>7</v>
+      </c>
+      <c r="C241" t="s">
         <v>8</v>
       </c>
-      <c r="D240">
-        <v>0.35499999999999998</v>
-      </c>
-      <c r="E240">
-        <v>0</v>
-      </c>
-      <c r="F240">
-        <v>0.74399999999999999</v>
-      </c>
-    </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A241" t="s">
-        <v>26</v>
-      </c>
-      <c r="B241" t="s">
-        <v>7</v>
-      </c>
-      <c r="C241" t="s">
-        <v>27</v>
-      </c>
       <c r="D241">
-        <v>0.42099999999999999</v>
+        <v>0.104</v>
       </c>
       <c r="E241">
         <v>0</v>
       </c>
       <c r="F241">
-        <v>0.63700000000000001</v>
+        <v>1.7999999999999999E-2</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="B242" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C242" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D242">
-        <v>0.754</v>
+        <v>0.65800000000000003</v>
       </c>
       <c r="E242">
         <v>0</v>
       </c>
       <c r="F242">
-        <v>1.9019999999999999</v>
+        <v>1.728</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="B243" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C243" t="s">
+        <v>15</v>
+      </c>
+      <c r="D243">
+        <v>0.42399999999999999</v>
+      </c>
+      <c r="E243">
+        <v>0</v>
+      </c>
+      <c r="F243">
+        <v>1.0089999999999999</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A244" t="s">
+        <v>24</v>
+      </c>
+      <c r="B244" t="s">
+        <v>14</v>
+      </c>
+      <c r="C244" t="s">
         <v>8</v>
       </c>
-      <c r="D243">
-        <v>0.69</v>
-      </c>
-      <c r="E243">
-        <v>0</v>
-      </c>
-      <c r="F243">
-        <v>1.6850000000000001</v>
-      </c>
-    </row>
-    <row r="244" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A244" t="s">
-        <v>33</v>
-      </c>
-      <c r="B244" t="s">
-        <v>7</v>
-      </c>
-      <c r="C244" t="s">
-        <v>15</v>
-      </c>
       <c r="D244">
-        <v>0.56000000000000005</v>
+        <v>0.317</v>
       </c>
       <c r="E244">
         <v>0</v>
       </c>
       <c r="F244">
-        <v>1.304</v>
+        <v>0.79100000000000004</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="B245" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C245" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D245">
-        <v>0.153</v>
+        <v>0.26100000000000001</v>
       </c>
       <c r="E245">
         <v>0</v>
       </c>
       <c r="F245">
-        <v>0.122</v>
-      </c>
-    </row>
-    <row r="246" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>0.65500000000000003</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B246" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C246" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D246">
-        <v>0.312</v>
+        <v>7.2999999999999995E-2</v>
       </c>
       <c r="E246">
-        <v>0</v>
+        <v>4.8999999999999998E-3</v>
       </c>
       <c r="F246">
-        <v>0.73</v>
-      </c>
-    </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A247" t="s">
-        <v>16</v>
+        <v>0.13500000000000001</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A247" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="B247" t="s">
         <v>7</v>
       </c>
       <c r="C247" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D247">
-        <v>0.246</v>
+        <v>6.8000000000000005E-2</v>
       </c>
       <c r="E247">
-        <v>0</v>
+        <v>1.15E-2</v>
       </c>
       <c r="F247">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0.121</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B248" t="s">
         <v>7</v>
       </c>
       <c r="C248" t="s">
+        <v>8</v>
+      </c>
+      <c r="D248">
+        <v>0.34</v>
+      </c>
+      <c r="E248">
+        <v>0</v>
+      </c>
+      <c r="F248">
+        <v>0.70599999999999996</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A249" t="s">
+        <v>24</v>
+      </c>
+      <c r="B249" t="s">
+        <v>7</v>
+      </c>
+      <c r="C249" t="s">
         <v>27</v>
       </c>
-      <c r="D248">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E248">
-        <v>0</v>
-      </c>
-      <c r="F248">
-        <v>0.32100000000000001</v>
-      </c>
-    </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A249" t="s">
-        <v>16</v>
-      </c>
-      <c r="B249" t="s">
-        <v>7</v>
-      </c>
-      <c r="C249" t="s">
-        <v>8</v>
-      </c>
       <c r="D249">
-        <v>0.122</v>
+        <v>0.29099999999999998</v>
       </c>
       <c r="E249">
         <v>0</v>
       </c>
       <c r="F249">
-        <v>0.27800000000000002</v>
+        <v>0.60899999999999999</v>
       </c>
     </row>
     <row r="250" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
@@ -6035,164 +6033,164 @@
         <v>24</v>
       </c>
       <c r="B250" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C250" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D250">
-        <v>7.2999999999999995E-2</v>
+        <v>0.504</v>
       </c>
       <c r="E250">
-        <v>4.8999999999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="F250">
-        <v>0.13500000000000001</v>
+        <v>0.57999999999999996</v>
       </c>
     </row>
     <row r="251" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A251" s="2" t="s">
+      <c r="A251" t="s">
         <v>24</v>
       </c>
       <c r="B251" t="s">
         <v>7</v>
       </c>
       <c r="C251" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D251">
-        <v>6.8000000000000005E-2</v>
+        <v>0.30599999999999999</v>
       </c>
       <c r="E251">
-        <v>1.15E-2</v>
+        <v>0</v>
       </c>
       <c r="F251">
-        <v>0.121</v>
+        <v>0.255</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B252" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C252" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D252">
-        <v>9.1999999999999998E-2</v>
+        <v>0.7</v>
       </c>
       <c r="E252">
-        <v>2.0000000000000001E-4</v>
+        <v>0</v>
       </c>
       <c r="F252">
-        <v>0.19700000000000001</v>
+        <v>1.931</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A253" s="2" t="s">
-        <v>21</v>
+      <c r="A253" t="s">
+        <v>20</v>
       </c>
       <c r="B253" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C253" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D253">
-        <v>6.4000000000000001E-2</v>
+        <v>0.58399999999999996</v>
       </c>
       <c r="E253">
-        <v>1.95E-2</v>
+        <v>0</v>
       </c>
       <c r="F253">
-        <v>0.14899999999999999</v>
-      </c>
-    </row>
-    <row r="254" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>1.4650000000000001</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B254" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C254" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D254">
-        <v>0.126</v>
+        <v>0.185</v>
       </c>
       <c r="E254">
         <v>0</v>
       </c>
       <c r="F254">
-        <v>0.123</v>
+        <v>0.47699999999999998</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B255" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C255" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="D255">
-        <v>0.104</v>
+        <v>0.193</v>
       </c>
       <c r="E255">
         <v>0</v>
       </c>
       <c r="F255">
-        <v>1.7999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A256" t="s">
-        <v>24</v>
+        <v>0.44900000000000001</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A256" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="B256" t="s">
         <v>7</v>
       </c>
       <c r="C256" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D256">
-        <v>0.34</v>
+        <v>5.8000000000000003E-2</v>
       </c>
       <c r="E256">
-        <v>0</v>
+        <v>4.5999999999999999E-2</v>
       </c>
       <c r="F256">
-        <v>0.70599999999999996</v>
+        <v>9.5000000000000001E-2</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A257" t="s">
-        <v>24</v>
+      <c r="A257" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="B257" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C257" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="D257">
-        <v>0.29099999999999998</v>
+        <v>6.4000000000000001E-2</v>
       </c>
       <c r="E257">
-        <v>0</v>
+        <v>1.95E-2</v>
       </c>
       <c r="F257">
-        <v>0.60899999999999999</v>
-      </c>
-    </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.3">
+        <v>4.9000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B258" t="s">
         <v>7</v>
@@ -6201,18 +6199,18 @@
         <v>22</v>
       </c>
       <c r="D258">
-        <v>0.504</v>
+        <v>0.52300000000000002</v>
       </c>
       <c r="E258">
         <v>0</v>
       </c>
       <c r="F258">
-        <v>0.57999999999999996</v>
+        <v>0.95599999999999996</v>
       </c>
     </row>
     <row r="259" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B259" t="s">
         <v>7</v>
@@ -6221,136 +6219,136 @@
         <v>15</v>
       </c>
       <c r="D259">
-        <v>0.30599999999999999</v>
+        <v>0.40400000000000003</v>
       </c>
       <c r="E259">
         <v>0</v>
       </c>
       <c r="F259">
-        <v>0.255</v>
+        <v>0.65700000000000003</v>
       </c>
     </row>
     <row r="260" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A260" s="2" t="s">
+      <c r="A260" t="s">
         <v>20</v>
       </c>
       <c r="B260" t="s">
         <v>7</v>
       </c>
       <c r="C260" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D260">
-        <v>5.8000000000000003E-2</v>
+        <v>0.221</v>
       </c>
       <c r="E260">
-        <v>4.5999999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="F260">
-        <v>9.5000000000000001E-2</v>
+        <v>0.52500000000000002</v>
       </c>
     </row>
     <row r="261" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A261" s="2" t="s">
+      <c r="A261" t="s">
         <v>20</v>
       </c>
       <c r="B261" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C261" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="D261">
-        <v>6.4000000000000001E-2</v>
+        <v>0.21199999999999999</v>
       </c>
       <c r="E261">
-        <v>1.95E-2</v>
+        <v>0</v>
       </c>
       <c r="F261">
-        <v>4.9000000000000002E-2</v>
+        <v>0.46200000000000002</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B262" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C262" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D262">
-        <v>0.52300000000000002</v>
+        <v>0.67600000000000005</v>
       </c>
       <c r="E262">
         <v>0</v>
       </c>
       <c r="F262">
-        <v>0.95599999999999996</v>
-      </c>
-    </row>
-    <row r="263" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>1.847</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B263" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C263" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="D263">
-        <v>0.40400000000000003</v>
+        <v>0.64</v>
       </c>
       <c r="E263">
         <v>0</v>
       </c>
       <c r="F263">
-        <v>0.65700000000000003</v>
+        <v>1.7030000000000001</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B264" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C264" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D264">
-        <v>0.221</v>
+        <v>0.59199999999999997</v>
       </c>
       <c r="E264">
         <v>0</v>
       </c>
       <c r="F264">
-        <v>0.52500000000000002</v>
+        <v>1.516</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B265" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C265" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="D265">
-        <v>0.21199999999999999</v>
+        <v>0.13200000000000001</v>
       </c>
       <c r="E265">
         <v>0</v>
       </c>
       <c r="F265">
-        <v>0.46200000000000002</v>
-      </c>
-    </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>23</v>
       </c>
@@ -6370,7 +6368,7 @@
         <v>1.7689999999999999</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>23</v>
       </c>
@@ -6410,7 +6408,7 @@
         <v>0.45700000000000002</v>
       </c>
     </row>
-    <row r="269" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>23</v>
       </c>
@@ -6430,7 +6428,7 @@
         <v>0.10100000000000001</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>23</v>
       </c>
